--- a/12607922 (1).xlsx
+++ b/12607922 (1).xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -277,6 +277,27 @@
   </si>
   <si>
     <t>went to market,studied for ca,met friends at home</t>
+  </si>
+  <si>
+    <t>studied for ca,came back uni</t>
+  </si>
+  <si>
+    <t>one extra class,slept,was tired,didnt feel like doing anything,chill day</t>
+  </si>
+  <si>
+    <t>alot of classes,tired,not much</t>
+  </si>
+  <si>
+    <t>classes,study,roam campus at night</t>
+  </si>
+  <si>
+    <t>freshers,washed clothes,studied for dbms ca,didnt go to college</t>
+  </si>
+  <si>
+    <t>attended classes,gave ca,came home,stuck traffic</t>
+  </si>
+  <si>
+    <t>studied for ca,met friends at home</t>
   </si>
 </sst>
 </file>
@@ -2475,169 +2496,323 @@
       <c r="A23" s="12">
         <v>46271</v>
       </c>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="14" t="str">
+      <c r="B23" s="13">
+        <v>540</v>
+      </c>
+      <c r="C23" s="13">
+        <v>30</v>
+      </c>
+      <c r="D23" s="13">
+        <v>240</v>
+      </c>
+      <c r="E23" s="13">
+        <v>60</v>
+      </c>
+      <c r="F23" s="13">
+        <v>0</v>
+      </c>
+      <c r="G23" s="13">
+        <v>0</v>
+      </c>
+      <c r="H23" s="13">
+        <v>300</v>
+      </c>
+      <c r="I23" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="14" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J23" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="15"/>
-      <c r="L23" s="15"/>
-      <c r="M23" s="15"/>
-      <c r="N23" s="16"/>
-    </row>
-    <row r="24" spans="1:14">
+        <v>270</v>
+      </c>
+      <c r="K23" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L23" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M23" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="N23" s="16" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="24" ht="43.5" spans="1:14">
       <c r="A24" s="12">
         <v>46272</v>
       </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="14" t="str">
+      <c r="B24" s="13">
+        <v>480</v>
+      </c>
+      <c r="C24" s="13">
+        <v>40</v>
+      </c>
+      <c r="D24" s="13">
+        <v>60</v>
+      </c>
+      <c r="E24" s="13">
+        <v>30</v>
+      </c>
+      <c r="F24" s="13">
+        <v>150</v>
+      </c>
+      <c r="G24" s="13">
+        <v>3</v>
+      </c>
+      <c r="H24" s="13">
+        <v>240</v>
+      </c>
+      <c r="I24" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="14" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J24" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="15"/>
-      <c r="L24" s="15"/>
-      <c r="M24" s="15"/>
-      <c r="N24" s="16"/>
+        <v>440</v>
+      </c>
+      <c r="K24" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="L24" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M24" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="N24" s="16" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="12">
         <v>46273</v>
       </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="14" t="str">
+      <c r="B25" s="13">
+        <v>420</v>
+      </c>
+      <c r="C25" s="13">
+        <v>40</v>
+      </c>
+      <c r="D25" s="13">
+        <v>0</v>
+      </c>
+      <c r="E25" s="13">
+        <v>0</v>
+      </c>
+      <c r="F25" s="13">
+        <v>350</v>
+      </c>
+      <c r="G25" s="13">
+        <v>7</v>
+      </c>
+      <c r="H25" s="13">
+        <v>180</v>
+      </c>
+      <c r="I25" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="14" t="str">
+        <v>990</v>
+      </c>
+      <c r="J25" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="15"/>
-      <c r="L25" s="15"/>
-      <c r="M25" s="15"/>
-      <c r="N25" s="16"/>
-    </row>
-    <row r="26" spans="1:14">
+        <v>450</v>
+      </c>
+      <c r="K25" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="L25" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M25" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="N25" s="16" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="26" ht="29" spans="1:14">
       <c r="A26" s="12">
         <v>46274</v>
       </c>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="14" t="str">
+      <c r="B26" s="13">
+        <v>420</v>
+      </c>
+      <c r="C26" s="13">
+        <v>40</v>
+      </c>
+      <c r="D26" s="13">
+        <v>220</v>
+      </c>
+      <c r="E26" s="13">
+        <v>60</v>
+      </c>
+      <c r="F26" s="13">
+        <v>200</v>
+      </c>
+      <c r="G26" s="13">
+        <v>4</v>
+      </c>
+      <c r="H26" s="13">
+        <v>180</v>
+      </c>
+      <c r="I26" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="14" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J26" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="15"/>
-      <c r="L26" s="15"/>
-      <c r="M26" s="15"/>
-      <c r="N26" s="16"/>
-    </row>
-    <row r="27" spans="1:14">
+        <v>320</v>
+      </c>
+      <c r="K26" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L26" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M26" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="N26" s="16" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="27" ht="29" spans="1:14">
       <c r="A27" s="12">
         <v>46275</v>
       </c>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="14" t="str">
+      <c r="B27" s="13">
+        <v>540</v>
+      </c>
+      <c r="C27" s="13">
+        <v>40</v>
+      </c>
+      <c r="D27" s="13">
+        <v>300</v>
+      </c>
+      <c r="E27" s="13">
+        <v>40</v>
+      </c>
+      <c r="F27" s="13">
+        <v>0</v>
+      </c>
+      <c r="G27" s="13">
+        <v>3</v>
+      </c>
+      <c r="H27" s="13">
+        <v>300</v>
+      </c>
+      <c r="I27" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="14" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J27" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="15"/>
-      <c r="L27" s="15"/>
-      <c r="M27" s="15"/>
-      <c r="N27" s="16"/>
-    </row>
-    <row r="28" spans="1:14">
+        <v>220</v>
+      </c>
+      <c r="K27" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L27" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M27" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="N27" s="16" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="28" ht="29" spans="1:14">
       <c r="A28" s="12">
         <v>46276</v>
       </c>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="14" t="str">
+      <c r="B28" s="13">
+        <v>320</v>
+      </c>
+      <c r="C28" s="13">
+        <v>0</v>
+      </c>
+      <c r="D28" s="13">
+        <v>0</v>
+      </c>
+      <c r="E28" s="13">
+        <v>0</v>
+      </c>
+      <c r="F28" s="13">
+        <v>300</v>
+      </c>
+      <c r="G28" s="13">
+        <v>6</v>
+      </c>
+      <c r="H28" s="13">
+        <v>420</v>
+      </c>
+      <c r="I28" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="14" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J28" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="15"/>
-      <c r="L28" s="15"/>
-      <c r="M28" s="15"/>
-      <c r="N28" s="16"/>
-    </row>
-    <row r="29" spans="1:14">
+        <v>400</v>
+      </c>
+      <c r="K28" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L28" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="M28" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="N28" s="16" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="29" ht="29" spans="1:14">
       <c r="A29" s="12">
         <v>46277</v>
       </c>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="14" t="str">
+      <c r="B29" s="13">
+        <v>540</v>
+      </c>
+      <c r="C29" s="13">
+        <v>30</v>
+      </c>
+      <c r="D29" s="13">
+        <v>240</v>
+      </c>
+      <c r="E29" s="13">
+        <v>0</v>
+      </c>
+      <c r="F29" s="13">
+        <v>0</v>
+      </c>
+      <c r="G29" s="13">
+        <v>0</v>
+      </c>
+      <c r="H29" s="13">
+        <v>240</v>
+      </c>
+      <c r="I29" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="14" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J29" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="15"/>
-      <c r="L29" s="15"/>
-      <c r="M29" s="15"/>
-      <c r="N29" s="16"/>
+        <v>390</v>
+      </c>
+      <c r="K29" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="L29" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="M29" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="N29" s="16" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="12">

--- a/12607922 (1).xlsx
+++ b/12607922 (1).xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="91">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -298,6 +298,9 @@
   </si>
   <si>
     <t>studied for ca,met friends at home</t>
+  </si>
+  <si>
+    <t>came back hostel,studied,slept early</t>
   </si>
 </sst>
 </file>
@@ -2814,29 +2817,51 @@
         <v>89</v>
       </c>
     </row>
-    <row r="30" spans="1:14">
+    <row r="30" ht="29" spans="1:14">
       <c r="A30" s="12">
         <v>46278</v>
       </c>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="14" t="str">
+      <c r="B30" s="13">
+        <v>600</v>
+      </c>
+      <c r="C30" s="13">
+        <v>30</v>
+      </c>
+      <c r="D30" s="13">
+        <v>180</v>
+      </c>
+      <c r="E30" s="13">
+        <v>30</v>
+      </c>
+      <c r="F30" s="13">
+        <v>0</v>
+      </c>
+      <c r="G30" s="13">
+        <v>0</v>
+      </c>
+      <c r="H30" s="13">
+        <v>180</v>
+      </c>
+      <c r="I30" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="14" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J30" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="15"/>
-      <c r="L30" s="15"/>
-      <c r="M30" s="15"/>
-      <c r="N30" s="16"/>
+        <v>420</v>
+      </c>
+      <c r="K30" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="L30" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M30" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="N30" s="16" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="12">

--- a/12607922 (1).xlsx
+++ b/12607922 (1).xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6200" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="6800" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -301,6 +301,9 @@
   </si>
   <si>
     <t>came back hostel,studied,slept early</t>
+  </si>
+  <si>
+    <t>headache not well,studied for ca</t>
   </si>
 </sst>
 </file>
@@ -2867,25 +2870,47 @@
       <c r="A31" s="12">
         <v>46279</v>
       </c>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
-      <c r="I31" s="14" t="str">
+      <c r="B31" s="13">
+        <v>420</v>
+      </c>
+      <c r="C31" s="13">
+        <v>40</v>
+      </c>
+      <c r="D31" s="13">
+        <v>180</v>
+      </c>
+      <c r="E31" s="13">
+        <v>20</v>
+      </c>
+      <c r="F31" s="13">
+        <v>150</v>
+      </c>
+      <c r="G31" s="13">
+        <v>3</v>
+      </c>
+      <c r="H31" s="13">
+        <v>180</v>
+      </c>
+      <c r="I31" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="14" t="str">
+        <v>990</v>
+      </c>
+      <c r="J31" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="15"/>
-      <c r="L31" s="15"/>
-      <c r="M31" s="15"/>
-      <c r="N31" s="16"/>
+        <v>450</v>
+      </c>
+      <c r="K31" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="L31" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M31" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="N31" s="16" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="12">

--- a/12607922 (1).xlsx
+++ b/12607922 (1).xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6800" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="6200" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="95">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -304,6 +304,15 @@
   </si>
   <si>
     <t>headache not well,studied for ca</t>
+  </si>
+  <si>
+    <t>two classes cancelled,studied for ca,gave ca,roam campus</t>
+  </si>
+  <si>
+    <t>normal day,study,</t>
+  </si>
+  <si>
+    <t>nap,studied,slept early,tired</t>
   </si>
 </sst>
 </file>
@@ -2702,7 +2711,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H27" s="13">
         <v>300</v>
@@ -2912,77 +2921,143 @@
         <v>91</v>
       </c>
     </row>
-    <row r="32" spans="1:14">
+    <row r="32" ht="29" spans="1:14">
       <c r="A32" s="12">
         <v>46280</v>
       </c>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="14" t="str">
+      <c r="B32" s="13">
+        <v>480</v>
+      </c>
+      <c r="C32" s="13">
+        <v>40</v>
+      </c>
+      <c r="D32" s="13">
+        <v>180</v>
+      </c>
+      <c r="E32" s="13">
+        <v>30</v>
+      </c>
+      <c r="F32" s="13">
+        <v>250</v>
+      </c>
+      <c r="G32" s="13">
+        <v>5</v>
+      </c>
+      <c r="H32" s="13">
+        <v>240</v>
+      </c>
+      <c r="I32" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="14" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J32" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="15"/>
-      <c r="L32" s="15"/>
-      <c r="M32" s="15"/>
-      <c r="N32" s="16"/>
+        <v>220</v>
+      </c>
+      <c r="K32" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L32" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M32" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="N32" s="16" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="12">
         <v>46281</v>
       </c>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
-      <c r="I33" s="14" t="str">
+      <c r="B33" s="13">
+        <v>420</v>
+      </c>
+      <c r="C33" s="13">
+        <v>30</v>
+      </c>
+      <c r="D33" s="13">
+        <v>200</v>
+      </c>
+      <c r="E33" s="13">
+        <v>30</v>
+      </c>
+      <c r="F33" s="13">
+        <v>200</v>
+      </c>
+      <c r="G33" s="13">
+        <v>4</v>
+      </c>
+      <c r="H33" s="13">
+        <v>210</v>
+      </c>
+      <c r="I33" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="14" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J33" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="15"/>
-      <c r="L33" s="15"/>
-      <c r="M33" s="15"/>
-      <c r="N33" s="16"/>
+        <v>350</v>
+      </c>
+      <c r="K33" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="L33" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="M33" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="N33" s="16" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="12">
         <v>46282</v>
       </c>
-      <c r="B34" s="13"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="13"/>
-      <c r="I34" s="14" t="str">
+      <c r="B34" s="13">
+        <v>480</v>
+      </c>
+      <c r="C34" s="13">
+        <v>30</v>
+      </c>
+      <c r="D34" s="13">
+        <v>120</v>
+      </c>
+      <c r="E34" s="13">
+        <v>20</v>
+      </c>
+      <c r="F34" s="13">
+        <v>350</v>
+      </c>
+      <c r="G34" s="13">
+        <v>7</v>
+      </c>
+      <c r="H34" s="13">
+        <v>190</v>
+      </c>
+      <c r="I34" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="14" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J34" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="15"/>
-      <c r="L34" s="15"/>
-      <c r="M34" s="15"/>
-      <c r="N34" s="16"/>
+        <v>250</v>
+      </c>
+      <c r="K34" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="L34" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M34" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="N34" s="16" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" s="12">

--- a/12607922 (1).xlsx
+++ b/12607922 (1).xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6200" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="6800" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="98">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -313,6 +313,15 @@
   </si>
   <si>
     <t>nap,studied,slept early,tired</t>
+  </si>
+  <si>
+    <t>long day at college,studied for analytical ca</t>
+  </si>
+  <si>
+    <t>went ambala,gave ca in morning,went home,attended wedding</t>
+  </si>
+  <si>
+    <t>came back,studied roam campus at night</t>
   </si>
 </sst>
 </file>
@@ -3059,77 +3068,143 @@
         <v>94</v>
       </c>
     </row>
-    <row r="35" spans="1:14">
+    <row r="35" ht="29" spans="1:14">
       <c r="A35" s="12">
         <v>46283</v>
       </c>
-      <c r="B35" s="13"/>
-      <c r="C35" s="13"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
-      <c r="H35" s="13"/>
-      <c r="I35" s="14" t="str">
+      <c r="B35" s="13">
+        <v>480</v>
+      </c>
+      <c r="C35" s="13">
+        <v>40</v>
+      </c>
+      <c r="D35" s="13">
+        <v>180</v>
+      </c>
+      <c r="E35" s="13">
+        <v>0</v>
+      </c>
+      <c r="F35" s="13">
+        <v>300</v>
+      </c>
+      <c r="G35" s="13">
+        <v>6</v>
+      </c>
+      <c r="H35" s="13">
+        <v>180</v>
+      </c>
+      <c r="I35" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="14" t="str">
+        <v>1180</v>
+      </c>
+      <c r="J35" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="15"/>
-      <c r="L35" s="15"/>
-      <c r="M35" s="15"/>
-      <c r="N35" s="16"/>
-    </row>
-    <row r="36" spans="1:14">
+        <v>260</v>
+      </c>
+      <c r="K35" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="L35" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M35" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="N35" s="16" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="36" ht="43.5" spans="1:14">
       <c r="A36" s="12">
         <v>46284</v>
       </c>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="13"/>
-      <c r="I36" s="14" t="str">
+      <c r="B36" s="13">
+        <v>480</v>
+      </c>
+      <c r="C36" s="13">
+        <v>0</v>
+      </c>
+      <c r="D36" s="13">
+        <v>0</v>
+      </c>
+      <c r="E36" s="13">
+        <v>0</v>
+      </c>
+      <c r="F36" s="13">
+        <v>50</v>
+      </c>
+      <c r="G36" s="13">
+        <v>1</v>
+      </c>
+      <c r="H36" s="13">
+        <v>180</v>
+      </c>
+      <c r="I36" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="14" t="str">
+        <v>710</v>
+      </c>
+      <c r="J36" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="15"/>
-      <c r="L36" s="15"/>
-      <c r="M36" s="15"/>
-      <c r="N36" s="16"/>
-    </row>
-    <row r="37" spans="1:14">
+        <v>730</v>
+      </c>
+      <c r="K36" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L36" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M36" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="N36" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="37" ht="29" spans="1:14">
       <c r="A37" s="12">
         <v>46285</v>
       </c>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
-      <c r="I37" s="14" t="str">
+      <c r="B37" s="13">
+        <v>540</v>
+      </c>
+      <c r="C37" s="13">
+        <v>60</v>
+      </c>
+      <c r="D37" s="13">
+        <v>60</v>
+      </c>
+      <c r="E37" s="13">
+        <v>120</v>
+      </c>
+      <c r="F37" s="13">
+        <v>0</v>
+      </c>
+      <c r="G37" s="13">
+        <v>0</v>
+      </c>
+      <c r="H37" s="13">
+        <v>180</v>
+      </c>
+      <c r="I37" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="14" t="str">
+        <v>960</v>
+      </c>
+      <c r="J37" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="15"/>
-      <c r="L37" s="15"/>
-      <c r="M37" s="15"/>
-      <c r="N37" s="16"/>
+        <v>480</v>
+      </c>
+      <c r="K37" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L37" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M37" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="N37" s="16" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="12">

--- a/12607922 (1).xlsx
+++ b/12607922 (1).xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6800" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="6200" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="103">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -195,6 +195,24 @@
     <t>Satisfied</t>
   </si>
   <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>missing family,attend classes</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>practice coding</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>tired, didnt do much</t>
+  </si>
+  <si>
     <t>low</t>
   </si>
   <si>
@@ -231,13 +249,7 @@
     <t>Very Satisfied</t>
   </si>
   <si>
-    <t>Medium</t>
-  </si>
-  <si>
     <t>homesick, chit chat with roommates</t>
-  </si>
-  <si>
-    <t>Low</t>
   </si>
   <si>
     <t>felt like doing nothing,tired from classes</t>
@@ -322,6 +334,9 @@
   </si>
   <si>
     <t>came back,studied roam campus at night</t>
+  </si>
+  <si>
+    <t>studied for ca,roam campus with friends</t>
   </si>
 </sst>
 </file>
@@ -1604,7 +1619,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N401"/>
+  <dimension ref="A1:N404"/>
   <sheetFormatPr defaultColWidth="8.63636363636364" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="18.4545454545455" customWidth="1"/>
@@ -1736,36 +1751,34 @@
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="7">
-        <v>46254</v>
+        <v>46251</v>
       </c>
       <c r="B6" s="8">
-        <v>450</v>
+        <v>480</v>
       </c>
       <c r="C6" s="8">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="D6" s="8">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="E6" s="8">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="F6" s="8">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="G6" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H6" s="8">
-        <v>180</v>
+        <v>40</v>
       </c>
       <c r="I6" s="9">
-        <f t="shared" ref="I6:I69" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
-        <v>1140</v>
+        <v>1025</v>
       </c>
       <c r="J6" s="9">
-        <f>IF(I6="","",1440-I6)</f>
-        <v>300</v>
+        <v>415</v>
       </c>
       <c r="K6" s="10" t="s">
         <v>53</v>
@@ -1782,442 +1795,438 @@
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="12">
+        <v>46252</v>
+      </c>
+      <c r="B7" s="13">
+        <v>400</v>
+      </c>
+      <c r="C7" s="13">
+        <v>20</v>
+      </c>
+      <c r="D7" s="13">
+        <v>120</v>
+      </c>
+      <c r="E7" s="13">
+        <v>90</v>
+      </c>
+      <c r="F7" s="13">
+        <v>200</v>
+      </c>
+      <c r="G7" s="13">
+        <v>4</v>
+      </c>
+      <c r="H7" s="13">
+        <v>120</v>
+      </c>
+      <c r="I7" s="14">
+        <v>850</v>
+      </c>
+      <c r="J7" s="14">
+        <v>590</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L7" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M7" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="N7" s="16" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="12">
+        <v>46253</v>
+      </c>
+      <c r="B8" s="13">
+        <v>480</v>
+      </c>
+      <c r="C8" s="13">
+        <v>10</v>
+      </c>
+      <c r="D8" s="13">
+        <v>100</v>
+      </c>
+      <c r="E8" s="13">
+        <v>90</v>
+      </c>
+      <c r="F8" s="13">
+        <v>400</v>
+      </c>
+      <c r="G8" s="13">
+        <v>8</v>
+      </c>
+      <c r="H8" s="13">
+        <v>20</v>
+      </c>
+      <c r="I8" s="14">
+        <v>1100</v>
+      </c>
+      <c r="J8" s="14">
+        <v>340</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="L8" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="M8" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="N8" s="16" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B9" s="8">
+        <v>450</v>
+      </c>
+      <c r="C9" s="8">
+        <v>60</v>
+      </c>
+      <c r="D9" s="8">
+        <v>30</v>
+      </c>
+      <c r="E9" s="8">
+        <v>70</v>
+      </c>
+      <c r="F9" s="8">
+        <v>350</v>
+      </c>
+      <c r="G9" s="8">
+        <v>7</v>
+      </c>
+      <c r="H9" s="8">
+        <v>180</v>
+      </c>
+      <c r="I9" s="9">
+        <f>IF(SUM(B9:F9,H9)=0,"",SUM(B9:F9,H9))</f>
+        <v>1140</v>
+      </c>
+      <c r="J9" s="9">
+        <f>IF(I9="","",1440-I9)</f>
+        <v>300</v>
+      </c>
+      <c r="K9" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="L9" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="M9" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="N9" s="11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="12">
         <v>46255</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B10" s="13">
         <v>450</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C10" s="13">
         <v>60</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D10" s="13">
         <v>0</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E10" s="13">
         <v>60</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F10" s="13">
         <v>300</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G10" s="13">
         <v>6</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H10" s="13">
         <v>240</v>
       </c>
-      <c r="I7" s="14">
-        <f t="shared" si="0"/>
+      <c r="I10" s="14">
+        <f t="shared" ref="I10:I72" si="0">IF(SUM(B10:F10,H10)=0,"",SUM(B10:F10,H10))</f>
         <v>1110</v>
       </c>
-      <c r="J7" s="14">
-        <f t="shared" ref="J6:J69" si="1">IF(I7="","",1440-I7)</f>
+      <c r="J10" s="14">
+        <f t="shared" ref="J10:J72" si="1">IF(I10="","",1440-I10)</f>
         <v>330</v>
       </c>
-      <c r="K7" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="L7" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="M7" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="N7" s="16" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" ht="29" spans="1:14">
-      <c r="A8" s="12">
+      <c r="K10" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="L10" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="M10" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="N10" s="16" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" ht="29" spans="1:14">
+      <c r="A11" s="12">
         <v>46256</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B11" s="13">
         <v>660</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C11" s="13">
         <v>20</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D11" s="13">
         <v>0</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E11" s="13">
         <v>30</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F11" s="13">
         <v>0</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G11" s="13">
         <v>0</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H11" s="13">
         <v>240</v>
       </c>
-      <c r="I8" s="14">
+      <c r="I11" s="14">
         <f t="shared" si="0"/>
         <v>950</v>
       </c>
-      <c r="J8" s="14">
+      <c r="J11" s="14">
         <f t="shared" si="1"/>
         <v>490</v>
       </c>
-      <c r="K8" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="L8" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="M8" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="N8" s="16" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="12">
+      <c r="K11" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="L11" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="M11" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="N11" s="16" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="12">
         <v>46257</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B12" s="13">
         <v>660</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C12" s="13">
         <v>20</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D12" s="13">
         <v>90</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E12" s="13">
         <v>40</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F12" s="13">
         <v>0</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G12" s="13">
         <v>0</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H12" s="13">
         <v>240</v>
       </c>
-      <c r="I9" s="14">
+      <c r="I12" s="14">
         <f t="shared" si="0"/>
         <v>1050</v>
       </c>
-      <c r="J9" s="14">
+      <c r="J12" s="14">
         <f t="shared" si="1"/>
         <v>390</v>
       </c>
-      <c r="K9" s="15" t="s">
+      <c r="K12" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="L9" s="15" t="s">
+      <c r="L12" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="M9" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="N9" s="16" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" ht="29" spans="1:14">
-      <c r="A10" s="12">
+      <c r="M12" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="N12" s="16" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" ht="29" spans="1:14">
+      <c r="A13" s="12">
         <v>46258</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B13" s="13">
         <v>360</v>
       </c>
-      <c r="C10" s="13">
+      <c r="C13" s="13">
         <v>30</v>
       </c>
-      <c r="D10" s="13">
+      <c r="D13" s="13">
         <v>60</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E13" s="13">
         <v>30</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F13" s="13">
         <v>150</v>
       </c>
-      <c r="G10" s="13">
+      <c r="G13" s="13">
         <v>3</v>
       </c>
-      <c r="H10" s="13">
+      <c r="H13" s="13">
         <v>240</v>
       </c>
-      <c r="I10" s="14">
+      <c r="I13" s="14">
         <f t="shared" si="0"/>
         <v>870</v>
       </c>
-      <c r="J10" s="14">
+      <c r="J13" s="14">
         <f t="shared" si="1"/>
         <v>570</v>
       </c>
-      <c r="K10" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="L10" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="M10" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="N10" s="16" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="11" ht="29" spans="1:14">
-      <c r="A11" s="12">
+      <c r="K13" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="L13" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="M13" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="N13" s="16" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" ht="29" spans="1:14">
+      <c r="A14" s="12">
         <v>46259</v>
       </c>
-      <c r="B11" s="13">
+      <c r="B14" s="13">
         <v>420</v>
       </c>
-      <c r="C11" s="13">
+      <c r="C14" s="13">
         <v>100</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D14" s="13">
         <v>0</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E14" s="13">
         <v>0</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F14" s="13">
         <v>420</v>
       </c>
-      <c r="G11" s="13">
+      <c r="G14" s="13">
         <v>7</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H14" s="13">
         <v>120</v>
       </c>
-      <c r="I11" s="14">
+      <c r="I14" s="14">
         <f t="shared" si="0"/>
         <v>1060</v>
       </c>
-      <c r="J11" s="14">
+      <c r="J14" s="14">
         <f t="shared" si="1"/>
         <v>380</v>
       </c>
-      <c r="K11" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="L11" s="15" t="s">
+      <c r="K14" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="L14" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="M14" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="N14" s="16" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15" ht="29" spans="1:14">
+      <c r="A15" s="12">
+        <v>46260</v>
+      </c>
+      <c r="B15" s="13">
+        <v>480</v>
+      </c>
+      <c r="C15" s="13">
+        <v>100</v>
+      </c>
+      <c r="D15" s="13">
+        <v>120</v>
+      </c>
+      <c r="E15" s="13">
         <v>60</v>
       </c>
-      <c r="M11" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="N11" s="16" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="12" ht="29" spans="1:14">
-      <c r="A12" s="12">
-        <v>46260</v>
-      </c>
-      <c r="B12" s="13">
-        <v>480</v>
-      </c>
-      <c r="C12" s="13">
-        <v>100</v>
-      </c>
-      <c r="D12" s="13">
-        <v>120</v>
-      </c>
-      <c r="E12" s="13">
-        <v>60</v>
-      </c>
-      <c r="F12" s="13">
+      <c r="F15" s="13">
         <v>240</v>
       </c>
-      <c r="G12" s="13">
+      <c r="G15" s="13">
         <v>4</v>
       </c>
-      <c r="H12" s="13">
+      <c r="H15" s="13">
         <v>180</v>
       </c>
-      <c r="I12" s="14">
+      <c r="I15" s="14">
         <f t="shared" si="0"/>
         <v>1180</v>
       </c>
-      <c r="J12" s="14">
+      <c r="J15" s="14">
         <f t="shared" si="1"/>
         <v>260</v>
       </c>
-      <c r="K12" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="L12" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="M12" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="N12" s="16" t="s">
+      <c r="K15" s="15" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="12">
-        <v>46261</v>
-      </c>
-      <c r="B13" s="13">
-        <v>480</v>
-      </c>
-      <c r="C13" s="13">
-        <v>100</v>
-      </c>
-      <c r="D13" s="13">
-        <v>0</v>
-      </c>
-      <c r="E13" s="13">
-        <v>0</v>
-      </c>
-      <c r="F13" s="13">
-        <v>300</v>
-      </c>
-      <c r="G13" s="13">
-        <v>6</v>
-      </c>
-      <c r="H13" s="13">
-        <v>300</v>
-      </c>
-      <c r="I13" s="14">
-        <f t="shared" si="0"/>
-        <v>1180</v>
-      </c>
-      <c r="J13" s="14">
-        <f t="shared" si="1"/>
-        <v>260</v>
-      </c>
-      <c r="K13" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="L13" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="M13" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="N13" s="16" t="s">
+      <c r="L15" s="15" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="12">
-        <v>46262</v>
-      </c>
-      <c r="B14" s="13">
-        <v>480</v>
-      </c>
-      <c r="C14" s="13">
-        <v>60</v>
-      </c>
-      <c r="D14" s="13">
-        <v>120</v>
-      </c>
-      <c r="E14" s="13">
-        <v>60</v>
-      </c>
-      <c r="F14" s="13">
-        <v>0</v>
-      </c>
-      <c r="G14" s="13">
-        <v>0</v>
-      </c>
-      <c r="H14" s="13">
-        <v>180</v>
-      </c>
-      <c r="I14" s="14">
-        <f t="shared" si="0"/>
-        <v>900</v>
-      </c>
-      <c r="J14" s="14">
-        <f t="shared" si="1"/>
-        <v>540</v>
-      </c>
-      <c r="K14" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="L14" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="M14" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="N14" s="16" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="15" ht="29" spans="1:14">
-      <c r="A15" s="12">
-        <v>46263</v>
-      </c>
-      <c r="B15" s="13">
-        <v>600</v>
-      </c>
-      <c r="C15" s="13">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13">
-        <v>120</v>
-      </c>
-      <c r="E15" s="13">
-        <v>30</v>
-      </c>
-      <c r="F15" s="13">
-        <v>0</v>
-      </c>
-      <c r="G15" s="13">
-        <v>0</v>
-      </c>
-      <c r="H15" s="13">
-        <v>120</v>
-      </c>
-      <c r="I15" s="14">
-        <f t="shared" si="0"/>
-        <v>890</v>
-      </c>
-      <c r="J15" s="14">
-        <f t="shared" si="1"/>
-        <v>550</v>
-      </c>
-      <c r="K15" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="L15" s="15" t="s">
-        <v>54</v>
-      </c>
       <c r="M15" s="15" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="N15" s="16" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="16" ht="43.5" spans="1:14">
+    <row r="16" spans="1:14">
       <c r="A16" s="12">
-        <v>46264</v>
+        <v>46261</v>
       </c>
       <c r="B16" s="13">
-        <v>600</v>
+        <v>480</v>
       </c>
       <c r="C16" s="13">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="D16" s="13">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="E16" s="13">
         <v>0</v>
       </c>
       <c r="F16" s="13">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G16" s="13">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H16" s="13">
-        <v>420</v>
+        <v>300</v>
       </c>
       <c r="I16" s="14">
         <f t="shared" si="0"/>
@@ -2228,36 +2237,36 @@
         <v>260</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="M16" s="15" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="N16" s="16" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="17" ht="43.5" spans="1:14">
+    <row r="17" spans="1:14">
       <c r="A17" s="12">
-        <v>46265</v>
+        <v>46262</v>
       </c>
       <c r="B17" s="13">
-        <v>600</v>
+        <v>480</v>
       </c>
       <c r="C17" s="13">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D17" s="13">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="E17" s="13">
         <v>60</v>
       </c>
       <c r="F17" s="13">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G17" s="13">
         <v>0</v>
@@ -2267,77 +2276,77 @@
       </c>
       <c r="I17" s="14">
         <f t="shared" si="0"/>
-        <v>1360</v>
+        <v>900</v>
       </c>
       <c r="J17" s="14">
         <f t="shared" si="1"/>
-        <v>80</v>
+        <v>540</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M17" s="15" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="N17" s="16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" ht="29" spans="1:14">
       <c r="A18" s="12">
-        <v>46266</v>
+        <v>46263</v>
       </c>
       <c r="B18" s="13">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="C18" s="13">
+        <v>20</v>
+      </c>
+      <c r="D18" s="13">
+        <v>120</v>
+      </c>
+      <c r="E18" s="13">
         <v>30</v>
       </c>
-      <c r="D18" s="13">
-        <v>30</v>
-      </c>
-      <c r="E18" s="13">
-        <v>20</v>
-      </c>
       <c r="F18" s="13">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="G18" s="13">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H18" s="13">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="I18" s="14">
         <f t="shared" si="0"/>
-        <v>1130</v>
+        <v>890</v>
       </c>
       <c r="J18" s="14">
         <f t="shared" si="1"/>
-        <v>310</v>
+        <v>550</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="M18" s="15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N18" s="16" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="19" ht="43.5" spans="1:14">
       <c r="A19" s="12">
-        <v>46267</v>
+        <v>46264</v>
       </c>
       <c r="B19" s="13">
-        <v>440</v>
+        <v>600</v>
       </c>
       <c r="C19" s="13">
         <v>40</v>
@@ -2346,139 +2355,139 @@
         <v>120</v>
       </c>
       <c r="E19" s="13">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F19" s="13">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="G19" s="13">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H19" s="13">
-        <v>240</v>
+        <v>420</v>
       </c>
       <c r="I19" s="14">
         <f t="shared" si="0"/>
-        <v>1110</v>
+        <v>1180</v>
       </c>
       <c r="J19" s="14">
         <f t="shared" si="1"/>
-        <v>330</v>
+        <v>260</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="M19" s="15" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="N19" s="16" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="20" ht="29" spans="1:14">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" ht="43.5" spans="1:14">
       <c r="A20" s="12">
-        <v>46268</v>
+        <v>46265</v>
       </c>
       <c r="B20" s="13">
-        <v>420</v>
+        <v>600</v>
       </c>
       <c r="C20" s="13">
         <v>40</v>
       </c>
       <c r="D20" s="13">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="E20" s="13">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F20" s="13">
-        <v>420</v>
+        <v>180</v>
       </c>
       <c r="G20" s="13">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H20" s="13">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="I20" s="14">
         <f t="shared" si="0"/>
-        <v>1110</v>
+        <v>1360</v>
       </c>
       <c r="J20" s="14">
         <f t="shared" si="1"/>
-        <v>330</v>
+        <v>80</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="M20" s="15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N20" s="16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" ht="29" spans="1:14">
       <c r="A21" s="12">
-        <v>46269</v>
+        <v>46266</v>
       </c>
       <c r="B21" s="13">
-        <v>480</v>
+        <v>450</v>
       </c>
       <c r="C21" s="13">
         <v>30</v>
       </c>
       <c r="D21" s="13">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E21" s="13">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F21" s="13">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="G21" s="13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H21" s="13">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="I21" s="14">
         <f t="shared" si="0"/>
-        <v>1070</v>
+        <v>1130</v>
       </c>
       <c r="J21" s="14">
         <f t="shared" si="1"/>
-        <v>370</v>
+        <v>310</v>
       </c>
       <c r="K21" s="15" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L21" s="15" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="M21" s="15" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="N21" s="16" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="22" ht="29" spans="1:14">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" s="12">
-        <v>46270</v>
+        <v>46267</v>
       </c>
       <c r="B22" s="13">
-        <v>600</v>
+        <v>440</v>
       </c>
       <c r="C22" s="13">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D22" s="13">
         <v>120</v>
@@ -2487,274 +2496,274 @@
         <v>30</v>
       </c>
       <c r="F22" s="13">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="G22" s="13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H22" s="13">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="I22" s="14">
         <f t="shared" si="0"/>
-        <v>1080</v>
+        <v>1110</v>
       </c>
       <c r="J22" s="14">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>330</v>
       </c>
       <c r="K22" s="15" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="L22" s="15" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="M22" s="15" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="N22" s="16" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" ht="29" spans="1:14">
       <c r="A23" s="12">
-        <v>46271</v>
+        <v>46268</v>
       </c>
       <c r="B23" s="13">
-        <v>540</v>
+        <v>420</v>
       </c>
       <c r="C23" s="13">
+        <v>40</v>
+      </c>
+      <c r="D23" s="13">
+        <v>80</v>
+      </c>
+      <c r="E23" s="13">
         <v>30</v>
       </c>
-      <c r="D23" s="13">
-        <v>240</v>
-      </c>
-      <c r="E23" s="13">
-        <v>60</v>
-      </c>
       <c r="F23" s="13">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="G23" s="13">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H23" s="13">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="I23" s="14">
         <f t="shared" si="0"/>
-        <v>1170</v>
+        <v>1110</v>
       </c>
       <c r="J23" s="14">
         <f t="shared" si="1"/>
-        <v>270</v>
+        <v>330</v>
       </c>
       <c r="K23" s="15" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L23" s="15" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="M23" s="15" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="N23" s="16" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="24" ht="43.5" spans="1:14">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="24" ht="29" spans="1:14">
       <c r="A24" s="12">
-        <v>46272</v>
+        <v>46269</v>
       </c>
       <c r="B24" s="13">
         <v>480</v>
       </c>
       <c r="C24" s="13">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D24" s="13">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="E24" s="13">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F24" s="13">
-        <v>150</v>
+        <v>360</v>
       </c>
       <c r="G24" s="13">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H24" s="13">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="I24" s="14">
         <f t="shared" si="0"/>
-        <v>1000</v>
+        <v>1070</v>
       </c>
       <c r="J24" s="14">
         <f t="shared" si="1"/>
-        <v>440</v>
+        <v>370</v>
       </c>
       <c r="K24" s="15" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="L24" s="15" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="M24" s="15" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="N24" s="16" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" ht="29" spans="1:14">
       <c r="A25" s="12">
-        <v>46273</v>
+        <v>46270</v>
       </c>
       <c r="B25" s="13">
-        <v>420</v>
+        <v>600</v>
       </c>
       <c r="C25" s="13">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D25" s="13">
+        <v>120</v>
+      </c>
+      <c r="E25" s="13">
+        <v>30</v>
+      </c>
+      <c r="F25" s="13">
         <v>0</v>
       </c>
-      <c r="E25" s="13">
+      <c r="G25" s="13">
         <v>0</v>
       </c>
-      <c r="F25" s="13">
-        <v>350</v>
-      </c>
-      <c r="G25" s="13">
-        <v>7</v>
-      </c>
       <c r="H25" s="13">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="I25" s="14">
         <f t="shared" si="0"/>
-        <v>990</v>
+        <v>1080</v>
       </c>
       <c r="J25" s="14">
         <f t="shared" si="1"/>
-        <v>450</v>
+        <v>360</v>
       </c>
       <c r="K25" s="15" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="L25" s="15" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="M25" s="15" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="N25" s="16" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="26" ht="29" spans="1:14">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" s="12">
-        <v>46274</v>
+        <v>46271</v>
       </c>
       <c r="B26" s="13">
-        <v>420</v>
+        <v>540</v>
       </c>
       <c r="C26" s="13">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D26" s="13">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="E26" s="13">
         <v>60</v>
       </c>
       <c r="F26" s="13">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G26" s="13">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H26" s="13">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="I26" s="14">
         <f t="shared" si="0"/>
-        <v>1120</v>
+        <v>1170</v>
       </c>
       <c r="J26" s="14">
         <f t="shared" si="1"/>
-        <v>320</v>
+        <v>270</v>
       </c>
       <c r="K26" s="15" t="s">
         <v>53</v>
       </c>
       <c r="L26" s="15" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="M26" s="15" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="N26" s="16" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="27" ht="29" spans="1:14">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="27" ht="43.5" spans="1:14">
       <c r="A27" s="12">
-        <v>46275</v>
+        <v>46272</v>
       </c>
       <c r="B27" s="13">
-        <v>540</v>
+        <v>480</v>
       </c>
       <c r="C27" s="13">
         <v>40</v>
       </c>
       <c r="D27" s="13">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="E27" s="13">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F27" s="13">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="G27" s="13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H27" s="13">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="I27" s="14">
         <f t="shared" si="0"/>
-        <v>1220</v>
+        <v>1000</v>
       </c>
       <c r="J27" s="14">
         <f t="shared" si="1"/>
-        <v>220</v>
+        <v>440</v>
       </c>
       <c r="K27" s="15" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L27" s="15" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="M27" s="15" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="N27" s="16" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="28" ht="29" spans="1:14">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" s="12">
-        <v>46276</v>
+        <v>46273</v>
       </c>
       <c r="B28" s="13">
-        <v>320</v>
+        <v>420</v>
       </c>
       <c r="C28" s="13">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D28" s="13">
         <v>0</v>
@@ -2763,96 +2772,96 @@
         <v>0</v>
       </c>
       <c r="F28" s="13">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="G28" s="13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H28" s="13">
-        <v>420</v>
+        <v>180</v>
       </c>
       <c r="I28" s="14">
         <f t="shared" si="0"/>
-        <v>1040</v>
+        <v>990</v>
       </c>
       <c r="J28" s="14">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="K28" s="15" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="L28" s="15" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="M28" s="15" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="N28" s="16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" ht="29" spans="1:14">
       <c r="A29" s="12">
-        <v>46277</v>
+        <v>46274</v>
       </c>
       <c r="B29" s="13">
-        <v>540</v>
+        <v>420</v>
       </c>
       <c r="C29" s="13">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D29" s="13">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="E29" s="13">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F29" s="13">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G29" s="13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H29" s="13">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="I29" s="14">
         <f t="shared" si="0"/>
-        <v>1050</v>
+        <v>1120</v>
       </c>
       <c r="J29" s="14">
         <f t="shared" si="1"/>
-        <v>390</v>
+        <v>320</v>
       </c>
       <c r="K29" s="15" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="L29" s="15" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="M29" s="15" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="N29" s="16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="30" ht="29" spans="1:14">
       <c r="A30" s="12">
-        <v>46278</v>
+        <v>46275</v>
       </c>
       <c r="B30" s="13">
-        <v>600</v>
+        <v>540</v>
       </c>
       <c r="C30" s="13">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D30" s="13">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="E30" s="13">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F30" s="13">
         <v>0</v>
@@ -2861,216 +2870,216 @@
         <v>0</v>
       </c>
       <c r="H30" s="13">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="I30" s="14">
         <f t="shared" si="0"/>
-        <v>1020</v>
+        <v>1220</v>
       </c>
       <c r="J30" s="14">
         <f t="shared" si="1"/>
+        <v>220</v>
+      </c>
+      <c r="K30" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L30" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M30" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="N30" s="16" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="31" ht="29" spans="1:14">
+      <c r="A31" s="12">
+        <v>46276</v>
+      </c>
+      <c r="B31" s="13">
+        <v>320</v>
+      </c>
+      <c r="C31" s="13">
+        <v>0</v>
+      </c>
+      <c r="D31" s="13">
+        <v>0</v>
+      </c>
+      <c r="E31" s="13">
+        <v>0</v>
+      </c>
+      <c r="F31" s="13">
+        <v>300</v>
+      </c>
+      <c r="G31" s="13">
+        <v>6</v>
+      </c>
+      <c r="H31" s="13">
         <v>420</v>
-      </c>
-      <c r="K30" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="L30" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="M30" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="N30" s="16" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14">
-      <c r="A31" s="12">
-        <v>46279</v>
-      </c>
-      <c r="B31" s="13">
-        <v>420</v>
-      </c>
-      <c r="C31" s="13">
-        <v>40</v>
-      </c>
-      <c r="D31" s="13">
-        <v>180</v>
-      </c>
-      <c r="E31" s="13">
-        <v>20</v>
-      </c>
-      <c r="F31" s="13">
-        <v>150</v>
-      </c>
-      <c r="G31" s="13">
-        <v>3</v>
-      </c>
-      <c r="H31" s="13">
-        <v>180</v>
       </c>
       <c r="I31" s="14">
         <f t="shared" si="0"/>
-        <v>990</v>
+        <v>1040</v>
       </c>
       <c r="J31" s="14">
         <f t="shared" si="1"/>
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="K31" s="15" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="L31" s="15" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="M31" s="15" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="N31" s="16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32" ht="29" spans="1:14">
       <c r="A32" s="12">
-        <v>46280</v>
+        <v>46277</v>
       </c>
       <c r="B32" s="13">
-        <v>480</v>
+        <v>540</v>
       </c>
       <c r="C32" s="13">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D32" s="13">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="E32" s="13">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F32" s="13">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G32" s="13">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H32" s="13">
         <v>240</v>
       </c>
       <c r="I32" s="14">
         <f t="shared" si="0"/>
-        <v>1220</v>
+        <v>1050</v>
       </c>
       <c r="J32" s="14">
         <f t="shared" si="1"/>
-        <v>220</v>
+        <v>390</v>
       </c>
       <c r="K32" s="15" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="L32" s="15" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="M32" s="15" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="N32" s="16" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="33" ht="29" spans="1:14">
       <c r="A33" s="12">
-        <v>46281</v>
+        <v>46278</v>
       </c>
       <c r="B33" s="13">
-        <v>420</v>
+        <v>600</v>
       </c>
       <c r="C33" s="13">
         <v>30</v>
       </c>
       <c r="D33" s="13">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="E33" s="13">
         <v>30</v>
       </c>
       <c r="F33" s="13">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G33" s="13">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H33" s="13">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="I33" s="14">
         <f t="shared" si="0"/>
-        <v>1090</v>
+        <v>1020</v>
       </c>
       <c r="J33" s="14">
         <f t="shared" si="1"/>
-        <v>350</v>
+        <v>420</v>
       </c>
       <c r="K33" s="15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L33" s="15" t="s">
         <v>66</v>
       </c>
       <c r="M33" s="15" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="N33" s="16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="12">
-        <v>46282</v>
+        <v>46279</v>
       </c>
       <c r="B34" s="13">
-        <v>480</v>
+        <v>420</v>
       </c>
       <c r="C34" s="13">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D34" s="13">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="E34" s="13">
         <v>20</v>
       </c>
       <c r="F34" s="13">
-        <v>350</v>
+        <v>150</v>
       </c>
       <c r="G34" s="13">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H34" s="13">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="I34" s="14">
         <f t="shared" si="0"/>
-        <v>1190</v>
+        <v>990</v>
       </c>
       <c r="J34" s="14">
         <f t="shared" si="1"/>
-        <v>250</v>
+        <v>450</v>
       </c>
       <c r="K34" s="15" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="L34" s="15" t="s">
         <v>54</v>
       </c>
       <c r="M34" s="15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N34" s="16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="35" ht="29" spans="1:14">
       <c r="A35" s="12">
-        <v>46283</v>
+        <v>46280</v>
       </c>
       <c r="B35" s="13">
         <v>480</v>
@@ -3082,229 +3091,317 @@
         <v>180</v>
       </c>
       <c r="E35" s="13">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F35" s="13">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G35" s="13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H35" s="13">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="I35" s="14">
         <f t="shared" si="0"/>
-        <v>1180</v>
+        <v>1220</v>
       </c>
       <c r="J35" s="14">
         <f t="shared" si="1"/>
-        <v>260</v>
+        <v>220</v>
       </c>
       <c r="K35" s="15" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="L35" s="15" t="s">
         <v>54</v>
       </c>
       <c r="M35" s="15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N35" s="16" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="36" ht="43.5" spans="1:14">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36" s="12">
-        <v>46284</v>
+        <v>46281</v>
       </c>
       <c r="B36" s="13">
-        <v>480</v>
+        <v>420</v>
       </c>
       <c r="C36" s="13">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D36" s="13">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E36" s="13">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F36" s="13">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="G36" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H36" s="13">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="I36" s="14">
         <f t="shared" si="0"/>
-        <v>710</v>
+        <v>1090</v>
       </c>
       <c r="J36" s="14">
         <f t="shared" si="1"/>
-        <v>730</v>
+        <v>350</v>
       </c>
       <c r="K36" s="15" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="L36" s="15" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="M36" s="15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="N36" s="16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="37" ht="29" spans="1:14">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
       <c r="A37" s="12">
-        <v>46285</v>
+        <v>46282</v>
       </c>
       <c r="B37" s="13">
-        <v>540</v>
+        <v>480</v>
       </c>
       <c r="C37" s="13">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D37" s="13">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="E37" s="13">
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="F37" s="13">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="G37" s="13">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H37" s="13">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="I37" s="14">
         <f t="shared" si="0"/>
-        <v>960</v>
+        <v>1190</v>
       </c>
       <c r="J37" s="14">
         <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="K37" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="L37" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M37" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="N37" s="16" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="38" ht="29" spans="1:14">
+      <c r="A38" s="12">
+        <v>46283</v>
+      </c>
+      <c r="B38" s="13">
         <v>480</v>
       </c>
-      <c r="K37" s="15" t="s">
+      <c r="C38" s="13">
+        <v>40</v>
+      </c>
+      <c r="D38" s="13">
+        <v>180</v>
+      </c>
+      <c r="E38" s="13">
+        <v>0</v>
+      </c>
+      <c r="F38" s="13">
+        <v>300</v>
+      </c>
+      <c r="G38" s="13">
+        <v>6</v>
+      </c>
+      <c r="H38" s="13">
+        <v>180</v>
+      </c>
+      <c r="I38" s="14">
+        <f t="shared" si="0"/>
+        <v>1180</v>
+      </c>
+      <c r="J38" s="14">
+        <f t="shared" si="1"/>
+        <v>260</v>
+      </c>
+      <c r="K38" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="L38" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M38" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="N38" s="16" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="39" ht="43.5" spans="1:14">
+      <c r="A39" s="12">
+        <v>46284</v>
+      </c>
+      <c r="B39" s="13">
+        <v>480</v>
+      </c>
+      <c r="C39" s="13">
+        <v>0</v>
+      </c>
+      <c r="D39" s="13">
+        <v>0</v>
+      </c>
+      <c r="E39" s="13">
+        <v>0</v>
+      </c>
+      <c r="F39" s="13">
+        <v>50</v>
+      </c>
+      <c r="G39" s="13">
+        <v>1</v>
+      </c>
+      <c r="H39" s="13">
+        <v>180</v>
+      </c>
+      <c r="I39" s="14">
+        <f t="shared" si="0"/>
+        <v>710</v>
+      </c>
+      <c r="J39" s="14">
+        <f t="shared" si="1"/>
+        <v>730</v>
+      </c>
+      <c r="K39" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="L37" s="15" t="s">
+      <c r="L39" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M39" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="N39" s="16" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" ht="29" spans="1:14">
+      <c r="A40" s="12">
+        <v>46285</v>
+      </c>
+      <c r="B40" s="13">
+        <v>540</v>
+      </c>
+      <c r="C40" s="13">
         <v>60</v>
       </c>
-      <c r="M37" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="N37" s="16" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14">
-      <c r="A38" s="12">
+      <c r="D40" s="13">
+        <v>60</v>
+      </c>
+      <c r="E40" s="13">
+        <v>120</v>
+      </c>
+      <c r="F40" s="13">
+        <v>0</v>
+      </c>
+      <c r="G40" s="13">
+        <v>0</v>
+      </c>
+      <c r="H40" s="13">
+        <v>180</v>
+      </c>
+      <c r="I40" s="14">
+        <f t="shared" si="0"/>
+        <v>960</v>
+      </c>
+      <c r="J40" s="14">
+        <f t="shared" si="1"/>
+        <v>480</v>
+      </c>
+      <c r="K40" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L40" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="M40" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="N40" s="16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="41" ht="29" spans="1:14">
+      <c r="A41" s="12">
         <v>46286</v>
       </c>
-      <c r="B38" s="13"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
-      <c r="H38" s="13"/>
-      <c r="I38" s="14" t="str">
+      <c r="B41" s="13">
+        <v>400</v>
+      </c>
+      <c r="C41" s="13">
+        <v>35</v>
+      </c>
+      <c r="D41" s="13">
+        <v>120</v>
+      </c>
+      <c r="E41" s="13">
+        <v>60</v>
+      </c>
+      <c r="F41" s="13">
+        <v>150</v>
+      </c>
+      <c r="G41" s="13">
+        <v>3</v>
+      </c>
+      <c r="H41" s="13">
+        <v>130</v>
+      </c>
+      <c r="I41" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="14" t="str">
+        <v>895</v>
+      </c>
+      <c r="J41" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="15"/>
-      <c r="L38" s="15"/>
-      <c r="M38" s="15"/>
-      <c r="N38" s="16"/>
-    </row>
-    <row r="39" spans="1:14">
-      <c r="A39" s="12">
-        <v>46287</v>
-      </c>
-      <c r="B39" s="13"/>
-      <c r="C39" s="13"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
-      <c r="H39" s="13"/>
-      <c r="I39" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="15"/>
-      <c r="L39" s="15"/>
-      <c r="M39" s="15"/>
-      <c r="N39" s="16"/>
-    </row>
-    <row r="40" spans="1:14">
-      <c r="A40" s="12">
-        <v>46288</v>
-      </c>
-      <c r="B40" s="13"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="13"/>
-      <c r="H40" s="13"/>
-      <c r="I40" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="15"/>
-      <c r="L40" s="15"/>
-      <c r="M40" s="15"/>
-      <c r="N40" s="16"/>
-    </row>
-    <row r="41" spans="1:14">
-      <c r="A41" s="12">
-        <v>46289</v>
-      </c>
-      <c r="B41" s="13"/>
-      <c r="C41" s="13"/>
-      <c r="D41" s="13"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="13"/>
-      <c r="H41" s="13"/>
-      <c r="I41" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="15"/>
-      <c r="L41" s="15"/>
-      <c r="M41" s="15"/>
-      <c r="N41" s="16"/>
+        <v>545</v>
+      </c>
+      <c r="K41" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L41" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M41" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="N41" s="16" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="12">
-        <v>46290</v>
+        <v>46287</v>
       </c>
       <c r="B42" s="13"/>
       <c r="C42" s="13"/>
@@ -3328,7 +3425,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="12">
-        <v>46291</v>
+        <v>46288</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -3352,7 +3449,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="12">
-        <v>46292</v>
+        <v>46289</v>
       </c>
       <c r="B44" s="13"/>
       <c r="C44" s="13"/>
@@ -3376,7 +3473,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="12">
-        <v>46293</v>
+        <v>46290</v>
       </c>
       <c r="B45" s="13"/>
       <c r="C45" s="13"/>
@@ -3400,7 +3497,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="12">
-        <v>46294</v>
+        <v>46291</v>
       </c>
       <c r="B46" s="13"/>
       <c r="C46" s="13"/>
@@ -3424,7 +3521,7 @@
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="12">
-        <v>46295</v>
+        <v>46292</v>
       </c>
       <c r="B47" s="13"/>
       <c r="C47" s="13"/>
@@ -3447,7 +3544,9 @@
       <c r="N47" s="16"/>
     </row>
     <row r="48" spans="1:14">
-      <c r="A48" s="12"/>
+      <c r="A48" s="12">
+        <v>46293</v>
+      </c>
       <c r="B48" s="13"/>
       <c r="C48" s="13"/>
       <c r="D48" s="13"/>
@@ -3469,7 +3568,9 @@
       <c r="N48" s="16"/>
     </row>
     <row r="49" spans="1:14">
-      <c r="A49" s="12"/>
+      <c r="A49" s="12">
+        <v>46294</v>
+      </c>
       <c r="B49" s="13"/>
       <c r="C49" s="13"/>
       <c r="D49" s="13"/>
@@ -3491,7 +3592,9 @@
       <c r="N49" s="16"/>
     </row>
     <row r="50" spans="1:14">
-      <c r="A50" s="12"/>
+      <c r="A50" s="12">
+        <v>46295</v>
+      </c>
       <c r="B50" s="13"/>
       <c r="C50" s="13"/>
       <c r="D50" s="13"/>
@@ -3940,11 +4043,11 @@
       <c r="G70" s="13"/>
       <c r="H70" s="13"/>
       <c r="I70" s="14" t="str">
-        <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J70" s="14" t="str">
-        <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K70" s="15"/>
@@ -3962,11 +4065,11 @@
       <c r="G71" s="13"/>
       <c r="H71" s="13"/>
       <c r="I71" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J71" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K71" s="15"/>
@@ -3984,11 +4087,11 @@
       <c r="G72" s="13"/>
       <c r="H72" s="13"/>
       <c r="I72" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J72" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K72" s="15"/>
@@ -4006,11 +4109,11 @@
       <c r="G73" s="13"/>
       <c r="H73" s="13"/>
       <c r="I73" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="I73:I136" si="2">IF(SUM(B73:F73,H73)=0,"",SUM(B73:F73,H73))</f>
         <v/>
       </c>
       <c r="J73" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J73:J136" si="3">IF(I73="","",1440-I73)</f>
         <v/>
       </c>
       <c r="K73" s="15"/>
@@ -5348,11 +5451,11 @@
       <c r="G134" s="13"/>
       <c r="H134" s="13"/>
       <c r="I134" s="14" t="str">
-        <f t="shared" ref="I134:I197" si="4">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J134" s="14" t="str">
-        <f t="shared" ref="J134:J197" si="5">IF(I134="","",1440-I134)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K134" s="15"/>
@@ -5370,11 +5473,11 @@
       <c r="G135" s="13"/>
       <c r="H135" s="13"/>
       <c r="I135" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J135" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K135" s="15"/>
@@ -5392,11 +5495,11 @@
       <c r="G136" s="13"/>
       <c r="H136" s="13"/>
       <c r="I136" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J136" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K136" s="15"/>
@@ -5414,11 +5517,11 @@
       <c r="G137" s="13"/>
       <c r="H137" s="13"/>
       <c r="I137" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I137:I200" si="4">IF(SUM(B137:F137,H137)=0,"",SUM(B137:F137,H137))</f>
         <v/>
       </c>
       <c r="J137" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J137:J200" si="5">IF(I137="","",1440-I137)</f>
         <v/>
       </c>
       <c r="K137" s="15"/>
@@ -6756,11 +6859,11 @@
       <c r="G198" s="13"/>
       <c r="H198" s="13"/>
       <c r="I198" s="14" t="str">
-        <f t="shared" ref="I198:I261" si="6">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J198" s="14" t="str">
-        <f t="shared" ref="J198:J261" si="7">IF(I198="","",1440-I198)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K198" s="15"/>
@@ -6778,11 +6881,11 @@
       <c r="G199" s="13"/>
       <c r="H199" s="13"/>
       <c r="I199" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J199" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K199" s="15"/>
@@ -6800,11 +6903,11 @@
       <c r="G200" s="13"/>
       <c r="H200" s="13"/>
       <c r="I200" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J200" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K200" s="15"/>
@@ -6822,11 +6925,11 @@
       <c r="G201" s="13"/>
       <c r="H201" s="13"/>
       <c r="I201" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I201:I264" si="6">IF(SUM(B201:F201,H201)=0,"",SUM(B201:F201,H201))</f>
         <v/>
       </c>
       <c r="J201" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J201:J264" si="7">IF(I201="","",1440-I201)</f>
         <v/>
       </c>
       <c r="K201" s="15"/>
@@ -8164,11 +8267,11 @@
       <c r="G262" s="13"/>
       <c r="H262" s="13"/>
       <c r="I262" s="14" t="str">
-        <f t="shared" ref="I262:I325" si="8">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J262" s="14" t="str">
-        <f t="shared" ref="J262:J325" si="9">IF(I262="","",1440-I262)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K262" s="15"/>
@@ -8186,11 +8289,11 @@
       <c r="G263" s="13"/>
       <c r="H263" s="13"/>
       <c r="I263" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J263" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K263" s="15"/>
@@ -8208,11 +8311,11 @@
       <c r="G264" s="13"/>
       <c r="H264" s="13"/>
       <c r="I264" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J264" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K264" s="15"/>
@@ -8230,11 +8333,11 @@
       <c r="G265" s="13"/>
       <c r="H265" s="13"/>
       <c r="I265" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I265:I328" si="8">IF(SUM(B265:F265,H265)=0,"",SUM(B265:F265,H265))</f>
         <v/>
       </c>
       <c r="J265" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J265:J328" si="9">IF(I265="","",1440-I265)</f>
         <v/>
       </c>
       <c r="K265" s="15"/>
@@ -9572,11 +9675,11 @@
       <c r="G326" s="13"/>
       <c r="H326" s="13"/>
       <c r="I326" s="14" t="str">
-        <f t="shared" ref="I326:I389" si="10">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J326" s="14" t="str">
-        <f t="shared" ref="J326:J389" si="11">IF(I326="","",1440-I326)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K326" s="15"/>
@@ -9594,11 +9697,11 @@
       <c r="G327" s="13"/>
       <c r="H327" s="13"/>
       <c r="I327" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J327" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K327" s="15"/>
@@ -9616,11 +9719,11 @@
       <c r="G328" s="13"/>
       <c r="H328" s="13"/>
       <c r="I328" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J328" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K328" s="15"/>
@@ -9638,11 +9741,11 @@
       <c r="G329" s="13"/>
       <c r="H329" s="13"/>
       <c r="I329" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I329:I392" si="10">IF(SUM(B329:F329,H329)=0,"",SUM(B329:F329,H329))</f>
         <v/>
       </c>
       <c r="J329" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J329:J392" si="11">IF(I329="","",1440-I329)</f>
         <v/>
       </c>
       <c r="K329" s="15"/>
@@ -10980,11 +11083,11 @@
       <c r="G390" s="13"/>
       <c r="H390" s="13"/>
       <c r="I390" s="14" t="str">
-        <f t="shared" ref="I390:I453" si="12">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J390" s="14" t="str">
-        <f t="shared" ref="J390:J453" si="13">IF(I390="","",1440-I390)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K390" s="15"/>
@@ -11002,11 +11105,11 @@
       <c r="G391" s="13"/>
       <c r="H391" s="13"/>
       <c r="I391" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J391" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K391" s="15"/>
@@ -11024,11 +11127,11 @@
       <c r="G392" s="13"/>
       <c r="H392" s="13"/>
       <c r="I392" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J392" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K392" s="15"/>
@@ -11046,11 +11149,11 @@
       <c r="G393" s="13"/>
       <c r="H393" s="13"/>
       <c r="I393" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="I393:I456" si="12">IF(SUM(B393:F393,H393)=0,"",SUM(B393:F393,H393))</f>
         <v/>
       </c>
       <c r="J393" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="J393:J456" si="13">IF(I393="","",1440-I393)</f>
         <v/>
       </c>
       <c r="K393" s="15"/>
@@ -11234,6 +11337,72 @@
       <c r="M401" s="15"/>
       <c r="N401" s="16"/>
     </row>
+    <row r="402" spans="1:14">
+      <c r="A402" s="12"/>
+      <c r="B402" s="13"/>
+      <c r="C402" s="13"/>
+      <c r="D402" s="13"/>
+      <c r="E402" s="13"/>
+      <c r="F402" s="13"/>
+      <c r="G402" s="13"/>
+      <c r="H402" s="13"/>
+      <c r="I402" s="14" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J402" s="14" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K402" s="15"/>
+      <c r="L402" s="15"/>
+      <c r="M402" s="15"/>
+      <c r="N402" s="16"/>
+    </row>
+    <row r="403" spans="1:14">
+      <c r="A403" s="12"/>
+      <c r="B403" s="13"/>
+      <c r="C403" s="13"/>
+      <c r="D403" s="13"/>
+      <c r="E403" s="13"/>
+      <c r="F403" s="13"/>
+      <c r="G403" s="13"/>
+      <c r="H403" s="13"/>
+      <c r="I403" s="14" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J403" s="14" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K403" s="15"/>
+      <c r="L403" s="15"/>
+      <c r="M403" s="15"/>
+      <c r="N403" s="16"/>
+    </row>
+    <row r="404" spans="1:14">
+      <c r="A404" s="12"/>
+      <c r="B404" s="13"/>
+      <c r="C404" s="13"/>
+      <c r="D404" s="13"/>
+      <c r="E404" s="13"/>
+      <c r="F404" s="13"/>
+      <c r="G404" s="13"/>
+      <c r="H404" s="13"/>
+      <c r="I404" s="14" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J404" s="14" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K404" s="15"/>
+      <c r="L404" s="15"/>
+      <c r="M404" s="15"/>
+      <c r="N404" s="16"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A1:N1"/>
@@ -11243,19 +11412,24 @@
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="A4:N4"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J401">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
+  <conditionalFormatting sqref="J9">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J6:J8 J10:J404">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K401">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6 K9 K7:K8 K10:K404">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L401">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6 L9 L7:L8 L10:L404">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6 M9 M7:M8 M10:M404">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>

--- a/12607922 (1).xlsx
+++ b/12607922 (1).xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="110">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -222,16 +222,13 @@
     <t>good</t>
   </si>
   <si>
-    <t>satisfied</t>
-  </si>
-  <si>
     <t>Attended fresher</t>
   </si>
   <si>
     <t>Neutral</t>
   </si>
   <si>
-    <t>Very Unsatisfied</t>
+    <t>Very Satisfied</t>
   </si>
   <si>
     <t>High</t>
@@ -244,9 +241,6 @@
   </si>
   <si>
     <t>Excellent</t>
-  </si>
-  <si>
-    <t>Very Satisfied</t>
   </si>
   <si>
     <t>homesick, chit chat with roommates</t>
@@ -337,6 +331,33 @@
   </si>
   <si>
     <t>studied for ca,roam campus with friends</t>
+  </si>
+  <si>
+    <t>studied for rnglish ca, roam campus</t>
+  </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>tired from classes,studied for dbms ca</t>
+  </si>
+  <si>
+    <t>attended classes,college protest started, luckily came home evening</t>
+  </si>
+  <si>
+    <t>college off,free at home,spending time with family,worked on python project</t>
+  </si>
+  <si>
+    <t>submitted report for project, watched series</t>
+  </si>
+  <si>
+    <t>college off,free at home,spending time with friends and family,watching series</t>
+  </si>
+  <si>
+    <t>college off,free at home,spending time with friends and family,watching series,found errors in my project solved them</t>
+  </si>
+  <si>
+    <t>college off,free at home,spending time with friends and family,watching series,started studying for MTE</t>
   </si>
 </sst>
 </file>
@@ -1964,13 +1985,13 @@
         <v>63</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="M10" s="15" t="s">
         <v>61</v>
       </c>
       <c r="N10" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" ht="29" spans="1:14">
@@ -2007,16 +2028,16 @@
         <v>490</v>
       </c>
       <c r="K11" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="L11" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="L11" s="15" t="s">
+      <c r="M11" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="M11" s="15" t="s">
+      <c r="N11" s="16" t="s">
         <v>68</v>
-      </c>
-      <c r="N11" s="16" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -2059,10 +2080,10 @@
         <v>54</v>
       </c>
       <c r="M12" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N12" s="16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" ht="29" spans="1:14">
@@ -2099,16 +2120,16 @@
         <v>570</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="M13" s="15" t="s">
         <v>57</v>
       </c>
       <c r="N13" s="16" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" ht="29" spans="1:14">
@@ -2148,13 +2169,13 @@
         <v>55</v>
       </c>
       <c r="L14" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M14" s="15" t="s">
         <v>55</v>
       </c>
       <c r="N14" s="16" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" ht="29" spans="1:14">
@@ -2191,16 +2212,16 @@
         <v>260</v>
       </c>
       <c r="K15" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L15" s="15" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="M15" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N15" s="16" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -2237,16 +2258,16 @@
         <v>260</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M16" s="15" t="s">
         <v>55</v>
       </c>
       <c r="N16" s="16" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -2283,16 +2304,16 @@
         <v>540</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="M17" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N17" s="16" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" ht="29" spans="1:14">
@@ -2329,16 +2350,16 @@
         <v>550</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L18" s="15" t="s">
         <v>54</v>
       </c>
       <c r="M18" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N18" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" ht="43.5" spans="1:14">
@@ -2375,16 +2396,16 @@
         <v>260</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M19" s="15" t="s">
         <v>55</v>
       </c>
       <c r="N19" s="16" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" ht="43.5" spans="1:14">
@@ -2421,16 +2442,16 @@
         <v>80</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="M20" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N20" s="16" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" ht="29" spans="1:14">
@@ -2470,13 +2491,13 @@
         <v>55</v>
       </c>
       <c r="L21" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M21" s="15" t="s">
         <v>55</v>
       </c>
       <c r="N21" s="16" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -2522,7 +2543,7 @@
         <v>57</v>
       </c>
       <c r="N22" s="16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" ht="29" spans="1:14">
@@ -2562,13 +2583,13 @@
         <v>55</v>
       </c>
       <c r="L23" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M23" s="15" t="s">
         <v>55</v>
       </c>
       <c r="N23" s="16" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" ht="29" spans="1:14">
@@ -2614,7 +2635,7 @@
         <v>55</v>
       </c>
       <c r="N24" s="16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" ht="29" spans="1:14">
@@ -2651,16 +2672,16 @@
         <v>360</v>
       </c>
       <c r="K25" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L25" s="15" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="M25" s="15" t="s">
         <v>57</v>
       </c>
       <c r="N25" s="16" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -2700,13 +2721,13 @@
         <v>53</v>
       </c>
       <c r="L26" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M26" s="15" t="s">
         <v>57</v>
       </c>
       <c r="N26" s="16" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" ht="43.5" spans="1:14">
@@ -2746,13 +2767,13 @@
         <v>55</v>
       </c>
       <c r="L27" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M27" s="15" t="s">
         <v>57</v>
       </c>
       <c r="N27" s="16" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -2789,7 +2810,7 @@
         <v>450</v>
       </c>
       <c r="K28" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L28" s="15" t="s">
         <v>54</v>
@@ -2798,7 +2819,7 @@
         <v>55</v>
       </c>
       <c r="N28" s="16" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29" ht="29" spans="1:14">
@@ -2841,10 +2862,10 @@
         <v>54</v>
       </c>
       <c r="M29" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N29" s="16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="30" ht="29" spans="1:14">
@@ -2887,10 +2908,10 @@
         <v>54</v>
       </c>
       <c r="M30" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N30" s="16" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="31" ht="29" spans="1:14">
@@ -2930,13 +2951,13 @@
         <v>53</v>
       </c>
       <c r="L31" s="15" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="M31" s="15" t="s">
         <v>55</v>
       </c>
       <c r="N31" s="16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="32" ht="29" spans="1:14">
@@ -2973,16 +2994,16 @@
         <v>390</v>
       </c>
       <c r="K32" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L32" s="15" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="M32" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N32" s="16" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="33" ht="29" spans="1:14">
@@ -3019,16 +3040,16 @@
         <v>420</v>
       </c>
       <c r="K33" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L33" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M33" s="15" t="s">
         <v>55</v>
       </c>
       <c r="N33" s="16" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34" spans="1:14">
@@ -3065,16 +3086,16 @@
         <v>450</v>
       </c>
       <c r="K34" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L34" s="15" t="s">
         <v>54</v>
       </c>
       <c r="M34" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N34" s="16" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="35" ht="29" spans="1:14">
@@ -3117,10 +3138,10 @@
         <v>54</v>
       </c>
       <c r="M35" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N35" s="16" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:14">
@@ -3157,16 +3178,16 @@
         <v>350</v>
       </c>
       <c r="K36" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L36" s="15" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="M36" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N36" s="16" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="37" spans="1:14">
@@ -3203,7 +3224,7 @@
         <v>250</v>
       </c>
       <c r="K37" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L37" s="15" t="s">
         <v>54</v>
@@ -3212,7 +3233,7 @@
         <v>55</v>
       </c>
       <c r="N37" s="16" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="38" ht="29" spans="1:14">
@@ -3249,7 +3270,7 @@
         <v>260</v>
       </c>
       <c r="K38" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L38" s="15" t="s">
         <v>54</v>
@@ -3258,7 +3279,7 @@
         <v>55</v>
       </c>
       <c r="N38" s="16" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="39" ht="43.5" spans="1:14">
@@ -3304,7 +3325,7 @@
         <v>57</v>
       </c>
       <c r="N39" s="16" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="40" ht="29" spans="1:14">
@@ -3344,13 +3365,13 @@
         <v>53</v>
       </c>
       <c r="L40" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M40" s="15" t="s">
         <v>57</v>
       </c>
       <c r="N40" s="16" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="41" ht="29" spans="1:14">
@@ -3393,318 +3414,614 @@
         <v>54</v>
       </c>
       <c r="M41" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N41" s="16" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" ht="29" spans="1:14">
       <c r="A42" s="12">
         <v>46287</v>
       </c>
-      <c r="B42" s="13"/>
-      <c r="C42" s="13"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="13"/>
-      <c r="H42" s="13"/>
-      <c r="I42" s="14" t="str">
+      <c r="B42" s="13">
+        <v>360</v>
+      </c>
+      <c r="C42" s="13">
+        <v>30</v>
+      </c>
+      <c r="D42" s="13">
+        <v>100</v>
+      </c>
+      <c r="E42" s="13">
+        <v>40</v>
+      </c>
+      <c r="F42" s="13">
+        <v>350</v>
+      </c>
+      <c r="G42" s="13">
+        <v>7</v>
+      </c>
+      <c r="H42" s="13">
+        <v>120</v>
+      </c>
+      <c r="I42" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="14" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J42" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="15"/>
-      <c r="L42" s="15"/>
-      <c r="M42" s="15"/>
-      <c r="N42" s="16"/>
-    </row>
-    <row r="43" spans="1:14">
+        <v>440</v>
+      </c>
+      <c r="K42" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="L42" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="M42" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="N42" s="16" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="43" ht="29" spans="1:14">
       <c r="A43" s="12">
         <v>46288</v>
       </c>
-      <c r="B43" s="13"/>
-      <c r="C43" s="13"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="13"/>
-      <c r="H43" s="13"/>
-      <c r="I43" s="14" t="str">
+      <c r="B43" s="13">
+        <v>300</v>
+      </c>
+      <c r="C43" s="13">
+        <v>30</v>
+      </c>
+      <c r="D43" s="13">
+        <v>200</v>
+      </c>
+      <c r="E43" s="13">
+        <v>30</v>
+      </c>
+      <c r="F43" s="13">
+        <v>200</v>
+      </c>
+      <c r="G43" s="13">
+        <v>4</v>
+      </c>
+      <c r="H43" s="13">
+        <v>180</v>
+      </c>
+      <c r="I43" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="14" t="str">
+        <v>940</v>
+      </c>
+      <c r="J43" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="15"/>
-      <c r="L43" s="15"/>
-      <c r="M43" s="15"/>
-      <c r="N43" s="16"/>
-    </row>
-    <row r="44" spans="1:14">
+        <v>500</v>
+      </c>
+      <c r="K43" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L43" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M43" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="N43" s="16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="44" ht="29" spans="1:14">
       <c r="A44" s="12">
         <v>46289</v>
       </c>
-      <c r="B44" s="13"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="13"/>
-      <c r="E44" s="13"/>
-      <c r="F44" s="13"/>
-      <c r="G44" s="13"/>
-      <c r="H44" s="13"/>
-      <c r="I44" s="14" t="str">
+      <c r="B44" s="13">
+        <v>380</v>
+      </c>
+      <c r="C44" s="13">
+        <v>40</v>
+      </c>
+      <c r="D44" s="13">
+        <v>180</v>
+      </c>
+      <c r="E44" s="13">
+        <v>20</v>
+      </c>
+      <c r="F44" s="13">
+        <v>350</v>
+      </c>
+      <c r="G44" s="13">
+        <v>7</v>
+      </c>
+      <c r="H44" s="13">
+        <v>180</v>
+      </c>
+      <c r="I44" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="14" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J44" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="15"/>
-      <c r="L44" s="15"/>
-      <c r="M44" s="15"/>
-      <c r="N44" s="16"/>
-    </row>
-    <row r="45" spans="1:14">
+        <v>290</v>
+      </c>
+      <c r="K44" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="L44" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="M44" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="N44" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="45" ht="43.5" spans="1:14">
       <c r="A45" s="12">
         <v>46290</v>
       </c>
-      <c r="B45" s="13"/>
-      <c r="C45" s="13"/>
-      <c r="D45" s="13"/>
-      <c r="E45" s="13"/>
-      <c r="F45" s="13"/>
-      <c r="G45" s="13"/>
-      <c r="H45" s="13"/>
-      <c r="I45" s="14" t="str">
+      <c r="B45" s="13">
+        <v>400</v>
+      </c>
+      <c r="C45" s="13">
+        <v>40</v>
+      </c>
+      <c r="D45" s="13">
+        <v>0</v>
+      </c>
+      <c r="E45" s="13">
+        <v>0</v>
+      </c>
+      <c r="F45" s="13">
+        <v>300</v>
+      </c>
+      <c r="G45" s="13">
+        <v>6</v>
+      </c>
+      <c r="H45" s="13">
+        <v>240</v>
+      </c>
+      <c r="I45" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="14" t="str">
+        <v>980</v>
+      </c>
+      <c r="J45" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="15"/>
-      <c r="L45" s="15"/>
-      <c r="M45" s="15"/>
-      <c r="N45" s="16"/>
-    </row>
-    <row r="46" spans="1:14">
+        <v>460</v>
+      </c>
+      <c r="K45" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L45" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="M45" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="N45" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="46" ht="43.5" spans="1:14">
       <c r="A46" s="12">
         <v>46291</v>
       </c>
-      <c r="B46" s="13"/>
-      <c r="C46" s="13"/>
-      <c r="D46" s="13"/>
-      <c r="E46" s="13"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="13"/>
-      <c r="H46" s="13"/>
-      <c r="I46" s="14" t="str">
+      <c r="B46" s="13">
+        <v>540</v>
+      </c>
+      <c r="C46" s="13">
+        <v>30</v>
+      </c>
+      <c r="D46" s="13">
+        <v>0</v>
+      </c>
+      <c r="E46" s="13">
+        <v>240</v>
+      </c>
+      <c r="F46" s="13">
+        <v>0</v>
+      </c>
+      <c r="G46" s="13">
+        <v>0</v>
+      </c>
+      <c r="H46" s="13">
+        <v>100</v>
+      </c>
+      <c r="I46" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="14" t="str">
+        <v>910</v>
+      </c>
+      <c r="J46" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="15"/>
-      <c r="L46" s="15"/>
-      <c r="M46" s="15"/>
-      <c r="N46" s="16"/>
-    </row>
-    <row r="47" spans="1:14">
+        <v>530</v>
+      </c>
+      <c r="K46" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="L46" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="M46" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="N46" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="47" ht="43.5" spans="1:14">
       <c r="A47" s="12">
         <v>46292</v>
       </c>
-      <c r="B47" s="13"/>
-      <c r="C47" s="13"/>
-      <c r="D47" s="13"/>
-      <c r="E47" s="13"/>
-      <c r="F47" s="13"/>
-      <c r="G47" s="13"/>
-      <c r="H47" s="13"/>
-      <c r="I47" s="14" t="str">
+      <c r="B47" s="13">
+        <v>500</v>
+      </c>
+      <c r="C47" s="13">
+        <v>30</v>
+      </c>
+      <c r="D47" s="13">
+        <v>0</v>
+      </c>
+      <c r="E47" s="13">
+        <v>160</v>
+      </c>
+      <c r="F47" s="13">
+        <v>0</v>
+      </c>
+      <c r="G47" s="13">
+        <v>0</v>
+      </c>
+      <c r="H47" s="13">
+        <v>120</v>
+      </c>
+      <c r="I47" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="14" t="str">
+        <v>810</v>
+      </c>
+      <c r="J47" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="15"/>
-      <c r="L47" s="15"/>
-      <c r="M47" s="15"/>
-      <c r="N47" s="16"/>
-    </row>
-    <row r="48" spans="1:14">
+        <v>630</v>
+      </c>
+      <c r="K47" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="L47" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="M47" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="N47" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="48" ht="29" spans="1:14">
       <c r="A48" s="12">
         <v>46293</v>
       </c>
-      <c r="B48" s="13"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="13"/>
-      <c r="E48" s="13"/>
-      <c r="F48" s="13"/>
-      <c r="G48" s="13"/>
-      <c r="H48" s="13"/>
-      <c r="I48" s="14" t="str">
+      <c r="B48" s="13">
+        <v>400</v>
+      </c>
+      <c r="C48" s="13">
+        <v>45</v>
+      </c>
+      <c r="D48" s="13">
+        <v>0</v>
+      </c>
+      <c r="E48" s="13">
+        <v>120</v>
+      </c>
+      <c r="F48" s="13">
+        <v>0</v>
+      </c>
+      <c r="G48" s="13">
+        <v>0</v>
+      </c>
+      <c r="H48" s="13">
+        <v>240</v>
+      </c>
+      <c r="I48" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="14" t="str">
+        <v>805</v>
+      </c>
+      <c r="J48" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="15"/>
-      <c r="L48" s="15"/>
-      <c r="M48" s="15"/>
-      <c r="N48" s="16"/>
-    </row>
-    <row r="49" spans="1:14">
+        <v>635</v>
+      </c>
+      <c r="K48" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="L48" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="M48" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="N48" s="16" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="49" ht="43.5" spans="1:14">
       <c r="A49" s="12">
         <v>46294</v>
       </c>
-      <c r="B49" s="13"/>
-      <c r="C49" s="13"/>
-      <c r="D49" s="13"/>
-      <c r="E49" s="13"/>
-      <c r="F49" s="13"/>
-      <c r="G49" s="13"/>
-      <c r="H49" s="13"/>
-      <c r="I49" s="14" t="str">
+      <c r="B49" s="13">
+        <v>480</v>
+      </c>
+      <c r="C49" s="13">
+        <v>20</v>
+      </c>
+      <c r="D49" s="13">
+        <v>0</v>
+      </c>
+      <c r="E49" s="13">
+        <v>0</v>
+      </c>
+      <c r="F49" s="13">
+        <v>0</v>
+      </c>
+      <c r="G49" s="13">
+        <v>0</v>
+      </c>
+      <c r="H49" s="13">
+        <v>180</v>
+      </c>
+      <c r="I49" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="14" t="str">
+        <v>680</v>
+      </c>
+      <c r="J49" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="15"/>
-      <c r="L49" s="15"/>
-      <c r="M49" s="15"/>
-      <c r="N49" s="16"/>
-    </row>
-    <row r="50" spans="1:14">
+        <v>760</v>
+      </c>
+      <c r="K49" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="L49" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="M49" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="N49" s="16" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="50" ht="43.5" spans="1:14">
       <c r="A50" s="12">
         <v>46295</v>
       </c>
-      <c r="B50" s="13"/>
-      <c r="C50" s="13"/>
-      <c r="D50" s="13"/>
-      <c r="E50" s="13"/>
-      <c r="F50" s="13"/>
-      <c r="G50" s="13"/>
-      <c r="H50" s="13"/>
-      <c r="I50" s="14" t="str">
+      <c r="B50" s="13">
+        <v>540</v>
+      </c>
+      <c r="C50" s="13">
+        <v>30</v>
+      </c>
+      <c r="D50" s="13">
+        <v>0</v>
+      </c>
+      <c r="E50" s="13">
+        <v>0</v>
+      </c>
+      <c r="F50" s="13">
+        <v>0</v>
+      </c>
+      <c r="G50" s="13">
+        <v>0</v>
+      </c>
+      <c r="H50" s="13">
+        <v>180</v>
+      </c>
+      <c r="I50" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="14" t="str">
+        <v>750</v>
+      </c>
+      <c r="J50" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="15"/>
-      <c r="L50" s="15"/>
-      <c r="M50" s="15"/>
-      <c r="N50" s="16"/>
-    </row>
-    <row r="51" spans="1:14">
-      <c r="A51" s="12"/>
-      <c r="B51" s="13"/>
-      <c r="C51" s="13"/>
-      <c r="D51" s="13"/>
-      <c r="E51" s="13"/>
-      <c r="F51" s="13"/>
-      <c r="G51" s="13"/>
-      <c r="H51" s="13"/>
-      <c r="I51" s="14" t="str">
+        <v>690</v>
+      </c>
+      <c r="K50" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="L50" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="M50" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="N50" s="16" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="51" ht="43.5" spans="1:14">
+      <c r="A51" s="12">
+        <v>46296</v>
+      </c>
+      <c r="B51" s="13">
+        <v>500</v>
+      </c>
+      <c r="C51" s="13">
+        <v>20</v>
+      </c>
+      <c r="D51" s="13">
+        <v>0</v>
+      </c>
+      <c r="E51" s="13">
+        <v>0</v>
+      </c>
+      <c r="F51" s="13">
+        <v>0</v>
+      </c>
+      <c r="G51" s="13">
+        <v>0</v>
+      </c>
+      <c r="H51" s="13">
+        <v>180</v>
+      </c>
+      <c r="I51" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="14" t="str">
+        <v>700</v>
+      </c>
+      <c r="J51" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="15"/>
-      <c r="L51" s="15"/>
-      <c r="M51" s="15"/>
-      <c r="N51" s="16"/>
-    </row>
-    <row r="52" spans="1:14">
-      <c r="A52" s="12"/>
-      <c r="B52" s="13"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="13"/>
-      <c r="E52" s="13"/>
-      <c r="F52" s="13"/>
-      <c r="G52" s="13"/>
-      <c r="H52" s="13"/>
-      <c r="I52" s="14" t="str">
+        <v>740</v>
+      </c>
+      <c r="K51" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="L51" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="M51" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="N51" s="16" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="52" ht="58" spans="1:14">
+      <c r="A52" s="12">
+        <v>46297</v>
+      </c>
+      <c r="B52" s="13">
+        <v>480</v>
+      </c>
+      <c r="C52" s="13">
+        <v>40</v>
+      </c>
+      <c r="D52" s="13">
+        <v>0</v>
+      </c>
+      <c r="E52" s="13">
+        <v>150</v>
+      </c>
+      <c r="F52" s="13">
+        <v>0</v>
+      </c>
+      <c r="G52" s="13">
+        <v>0</v>
+      </c>
+      <c r="H52" s="13">
+        <v>180</v>
+      </c>
+      <c r="I52" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="14" t="str">
+        <v>850</v>
+      </c>
+      <c r="J52" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="15"/>
-      <c r="L52" s="15"/>
-      <c r="M52" s="15"/>
-      <c r="N52" s="16"/>
-    </row>
-    <row r="53" spans="1:14">
-      <c r="A53" s="12"/>
-      <c r="B53" s="13"/>
-      <c r="C53" s="13"/>
-      <c r="D53" s="13"/>
-      <c r="E53" s="13"/>
-      <c r="F53" s="13"/>
-      <c r="G53" s="13"/>
-      <c r="H53" s="13"/>
-      <c r="I53" s="14" t="str">
+        <v>590</v>
+      </c>
+      <c r="K52" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="L52" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="M52" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="N52" s="16" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="53" ht="43.5" spans="1:14">
+      <c r="A53" s="12">
+        <v>46298</v>
+      </c>
+      <c r="B53" s="13">
+        <v>540</v>
+      </c>
+      <c r="C53" s="13">
+        <v>30</v>
+      </c>
+      <c r="D53" s="13">
+        <v>0</v>
+      </c>
+      <c r="E53" s="13">
+        <v>0</v>
+      </c>
+      <c r="F53" s="13">
+        <v>0</v>
+      </c>
+      <c r="G53" s="13">
+        <v>0</v>
+      </c>
+      <c r="H53" s="13">
+        <v>180</v>
+      </c>
+      <c r="I53" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="14" t="str">
+        <v>750</v>
+      </c>
+      <c r="J53" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="15"/>
-      <c r="L53" s="15"/>
-      <c r="M53" s="15"/>
-      <c r="N53" s="16"/>
-    </row>
-    <row r="54" spans="1:14">
-      <c r="A54" s="12"/>
-      <c r="B54" s="13"/>
-      <c r="C54" s="13"/>
-      <c r="D54" s="13"/>
-      <c r="E54" s="13"/>
-      <c r="F54" s="13"/>
-      <c r="G54" s="13"/>
-      <c r="H54" s="13"/>
-      <c r="I54" s="14" t="str">
+        <v>690</v>
+      </c>
+      <c r="K53" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="L53" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="M53" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="N53" s="16" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="54" ht="58" spans="1:14">
+      <c r="A54" s="12">
+        <v>46299</v>
+      </c>
+      <c r="B54" s="13">
+        <v>540</v>
+      </c>
+      <c r="C54" s="13">
+        <v>30</v>
+      </c>
+      <c r="D54" s="13">
+        <v>180</v>
+      </c>
+      <c r="E54" s="13">
+        <v>30</v>
+      </c>
+      <c r="F54" s="13">
+        <v>0</v>
+      </c>
+      <c r="G54" s="13">
+        <v>0</v>
+      </c>
+      <c r="H54" s="13">
+        <v>180</v>
+      </c>
+      <c r="I54" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="14" t="str">
+        <v>960</v>
+      </c>
+      <c r="J54" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="15"/>
-      <c r="L54" s="15"/>
-      <c r="M54" s="15"/>
-      <c r="N54" s="16"/>
+        <v>480</v>
+      </c>
+      <c r="K54" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="L54" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="M54" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="N54" s="16" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="55" spans="1:14">
-      <c r="A55" s="12"/>
+      <c r="A55" s="12">
+        <v>46300</v>
+      </c>
       <c r="B55" s="13"/>
       <c r="C55" s="13"/>
       <c r="D55" s="13"/>
@@ -11423,13 +11740,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6 K9 K7:K8 K10:K404">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K404">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6 L9 L7:L8 L10:L404">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L404">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6 M9 M7:M8 M10:M404">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M404">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>

--- a/12607922 (1).xlsx
+++ b/12607922 (1).xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6200" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="6800" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="113">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -358,6 +358,15 @@
   </si>
   <si>
     <t>college off,free at home,spending time with friends and family,watching series,started studying for MTE</t>
+  </si>
+  <si>
+    <t>online classes started,studied,met college friends</t>
+  </si>
+  <si>
+    <t>studied for MTE rest normal schedule</t>
+  </si>
+  <si>
+    <t>attended classes, outing with my college friends</t>
   </si>
 </sst>
 </file>
@@ -4018,73 +4027,143 @@
         <v>109</v>
       </c>
     </row>
-    <row r="55" spans="1:14">
+    <row r="55" ht="43.5" spans="1:14">
       <c r="A55" s="12">
         <v>46300</v>
       </c>
-      <c r="B55" s="13"/>
-      <c r="C55" s="13"/>
-      <c r="D55" s="13"/>
-      <c r="E55" s="13"/>
-      <c r="F55" s="13"/>
-      <c r="G55" s="13"/>
-      <c r="H55" s="13"/>
-      <c r="I55" s="14" t="str">
+      <c r="B55" s="13">
+        <v>400</v>
+      </c>
+      <c r="C55" s="13">
+        <v>30</v>
+      </c>
+      <c r="D55" s="13">
+        <v>120</v>
+      </c>
+      <c r="E55" s="13">
+        <v>0</v>
+      </c>
+      <c r="F55" s="13">
+        <v>150</v>
+      </c>
+      <c r="G55" s="13">
+        <v>3</v>
+      </c>
+      <c r="H55" s="13">
+        <v>300</v>
+      </c>
+      <c r="I55" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="14" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J55" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="15"/>
-      <c r="L55" s="15"/>
-      <c r="M55" s="15"/>
-      <c r="N55" s="16"/>
-    </row>
-    <row r="56" spans="1:14">
-      <c r="A56" s="12"/>
-      <c r="B56" s="13"/>
-      <c r="C56" s="13"/>
-      <c r="D56" s="13"/>
-      <c r="E56" s="13"/>
-      <c r="F56" s="13"/>
-      <c r="G56" s="13"/>
-      <c r="H56" s="13"/>
-      <c r="I56" s="14" t="str">
+        <v>440</v>
+      </c>
+      <c r="K55" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="L55" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="M55" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="N55" s="16" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="56" ht="29" spans="1:14">
+      <c r="A56" s="12">
+        <v>46301</v>
+      </c>
+      <c r="B56" s="13">
+        <v>550</v>
+      </c>
+      <c r="C56" s="13">
+        <v>30</v>
+      </c>
+      <c r="D56" s="13">
+        <v>60</v>
+      </c>
+      <c r="E56" s="13">
+        <v>0</v>
+      </c>
+      <c r="F56" s="13">
+        <v>350</v>
+      </c>
+      <c r="G56" s="13">
+        <v>7</v>
+      </c>
+      <c r="H56" s="13">
+        <v>120</v>
+      </c>
+      <c r="I56" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="14" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J56" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="15"/>
-      <c r="L56" s="15"/>
-      <c r="M56" s="15"/>
-      <c r="N56" s="16"/>
-    </row>
-    <row r="57" spans="1:14">
-      <c r="A57" s="12"/>
-      <c r="B57" s="13"/>
-      <c r="C57" s="13"/>
-      <c r="D57" s="13"/>
-      <c r="E57" s="13"/>
-      <c r="F57" s="13"/>
-      <c r="G57" s="13"/>
-      <c r="H57" s="13"/>
-      <c r="I57" s="14" t="str">
+        <v>330</v>
+      </c>
+      <c r="K56" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="L56" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="M56" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="N56" s="16" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="57" ht="29" spans="1:14">
+      <c r="A57" s="12">
+        <v>46302</v>
+      </c>
+      <c r="B57" s="13">
+        <v>540</v>
+      </c>
+      <c r="C57" s="13">
+        <v>30</v>
+      </c>
+      <c r="D57" s="13">
+        <v>0</v>
+      </c>
+      <c r="E57" s="13">
+        <v>0</v>
+      </c>
+      <c r="F57" s="13">
+        <v>200</v>
+      </c>
+      <c r="G57" s="13">
+        <v>4</v>
+      </c>
+      <c r="H57" s="13">
+        <v>240</v>
+      </c>
+      <c r="I57" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="14" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J57" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="15"/>
-      <c r="L57" s="15"/>
-      <c r="M57" s="15"/>
-      <c r="N57" s="16"/>
+        <v>430</v>
+      </c>
+      <c r="K57" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="L57" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="M57" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="N57" s="16" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="58" spans="1:14">
       <c r="A58" s="12"/>
@@ -11730,23 +11809,28 @@
     <mergeCell ref="A4:N4"/>
   </mergeCells>
   <conditionalFormatting sqref="J9">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J55:J57">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J6:J8 J10:J404">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
+  <conditionalFormatting sqref="J6:J8 J10:J54 J58:J404">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K404">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K54 K55:K57 K58:K404">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L404">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L54 L55:L57 L58:L404">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M404">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M54 M55:M57 M58:M404">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>

--- a/12607922 (1).xlsx
+++ b/12607922 (1).xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="129">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -367,6 +367,54 @@
   </si>
   <si>
     <t>attended classes, outing with my college friends</t>
+  </si>
+  <si>
+    <t>attended online class, studied for mte</t>
+  </si>
+  <si>
+    <t>preparing fo ca, going to college tomorrow, excited and nervous</t>
+  </si>
+  <si>
+    <t>came from home after long break,prepared fir first mte</t>
+  </si>
+  <si>
+    <t>gave 1 mte, rest, studied for mte2</t>
+  </si>
+  <si>
+    <t>cpp ca not good, feeling bad,prepared for dbms mte</t>
+  </si>
+  <si>
+    <t>good mte, rest , prepared for next</t>
+  </si>
+  <si>
+    <t>praepared for analytical mte, holiday today</t>
+  </si>
+  <si>
+    <t>mte went good, rest, studied for next</t>
+  </si>
+  <si>
+    <t>went home after last mte, travelled</t>
+  </si>
+  <si>
+    <t>full day chilling, watching series</t>
+  </si>
+  <si>
+    <t>did holiday, celeberated ashtmi, spent time with family</t>
+  </si>
+  <si>
+    <t>holiday of dusherra, went to see ravan dehan with family</t>
+  </si>
+  <si>
+    <t>came back to college, rest</t>
+  </si>
+  <si>
+    <t>attended classes,tired</t>
+  </si>
+  <si>
+    <t>felt low, roam campus at night</t>
+  </si>
+  <si>
+    <t>completed some pending work, washed clothes,saw movie</t>
   </si>
 </sst>
 </file>
@@ -4165,401 +4213,833 @@
         <v>112</v>
       </c>
     </row>
-    <row r="58" spans="1:14">
-      <c r="A58" s="12"/>
-      <c r="B58" s="13"/>
-      <c r="C58" s="13"/>
-      <c r="D58" s="13"/>
-      <c r="E58" s="13"/>
-      <c r="F58" s="13"/>
-      <c r="G58" s="13"/>
-      <c r="H58" s="13"/>
-      <c r="I58" s="14" t="str">
+    <row r="58" ht="29" spans="1:14">
+      <c r="A58" s="12">
+        <v>46303</v>
+      </c>
+      <c r="B58" s="13">
+        <v>420</v>
+      </c>
+      <c r="C58" s="13">
+        <v>20</v>
+      </c>
+      <c r="D58" s="13">
+        <v>120</v>
+      </c>
+      <c r="E58" s="13">
+        <v>30</v>
+      </c>
+      <c r="F58" s="13">
+        <v>300</v>
+      </c>
+      <c r="G58" s="13">
+        <v>6</v>
+      </c>
+      <c r="H58" s="13">
+        <v>240</v>
+      </c>
+      <c r="I58" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="14" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J58" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="15"/>
-      <c r="L58" s="15"/>
-      <c r="M58" s="15"/>
-      <c r="N58" s="16"/>
-    </row>
-    <row r="59" spans="1:14">
-      <c r="A59" s="12"/>
-      <c r="B59" s="13"/>
-      <c r="C59" s="13"/>
-      <c r="D59" s="13"/>
-      <c r="E59" s="13"/>
-      <c r="F59" s="13"/>
-      <c r="G59" s="13"/>
-      <c r="H59" s="13"/>
-      <c r="I59" s="14" t="str">
+        <v>310</v>
+      </c>
+      <c r="K58" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="L58" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="M58" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="N58" s="16" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="59" ht="29" spans="1:14">
+      <c r="A59" s="12">
+        <v>46304</v>
+      </c>
+      <c r="B59" s="13">
+        <v>480</v>
+      </c>
+      <c r="C59" s="13">
+        <v>35</v>
+      </c>
+      <c r="D59" s="13">
+        <v>180</v>
+      </c>
+      <c r="E59" s="13">
+        <v>60</v>
+      </c>
+      <c r="F59" s="13">
+        <v>350</v>
+      </c>
+      <c r="G59" s="13">
+        <v>7</v>
+      </c>
+      <c r="H59" s="13">
+        <v>180</v>
+      </c>
+      <c r="I59" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="14" t="str">
+        <v>1285</v>
+      </c>
+      <c r="J59" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="15"/>
-      <c r="L59" s="15"/>
-      <c r="M59" s="15"/>
-      <c r="N59" s="16"/>
-    </row>
-    <row r="60" spans="1:14">
-      <c r="A60" s="12"/>
-      <c r="B60" s="13"/>
-      <c r="C60" s="13"/>
-      <c r="D60" s="13"/>
-      <c r="E60" s="13"/>
-      <c r="F60" s="13"/>
-      <c r="G60" s="13"/>
-      <c r="H60" s="13"/>
-      <c r="I60" s="14" t="str">
+        <v>155</v>
+      </c>
+      <c r="K59" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L59" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="M59" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="N59" s="16" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="60" ht="29" spans="1:14">
+      <c r="A60" s="12">
+        <v>46305</v>
+      </c>
+      <c r="B60" s="13">
+        <v>360</v>
+      </c>
+      <c r="C60" s="13">
+        <v>40</v>
+      </c>
+      <c r="D60" s="13">
+        <v>270</v>
+      </c>
+      <c r="E60" s="13">
+        <v>60</v>
+      </c>
+      <c r="F60" s="13">
+        <v>0</v>
+      </c>
+      <c r="G60" s="13">
+        <v>0</v>
+      </c>
+      <c r="H60" s="13">
+        <v>180</v>
+      </c>
+      <c r="I60" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="14" t="str">
+        <v>910</v>
+      </c>
+      <c r="J60" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="15"/>
-      <c r="L60" s="15"/>
-      <c r="M60" s="15"/>
-      <c r="N60" s="16"/>
-    </row>
-    <row r="61" spans="1:14">
-      <c r="A61" s="12"/>
-      <c r="B61" s="13"/>
-      <c r="C61" s="13"/>
-      <c r="D61" s="13"/>
-      <c r="E61" s="13"/>
-      <c r="F61" s="13"/>
-      <c r="G61" s="13"/>
-      <c r="H61" s="13"/>
-      <c r="I61" s="14" t="str">
+        <v>530</v>
+      </c>
+      <c r="K60" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="L60" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="M60" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="N60" s="16" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="61" ht="29" spans="1:14">
+      <c r="A61" s="12">
+        <v>46306</v>
+      </c>
+      <c r="B61" s="13">
+        <v>380</v>
+      </c>
+      <c r="C61" s="13">
+        <v>30</v>
+      </c>
+      <c r="D61" s="13">
+        <v>360</v>
+      </c>
+      <c r="E61" s="13">
+        <v>0</v>
+      </c>
+      <c r="F61" s="13">
+        <v>0</v>
+      </c>
+      <c r="G61" s="13">
+        <v>0</v>
+      </c>
+      <c r="H61" s="13">
+        <v>270</v>
+      </c>
+      <c r="I61" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="14" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J61" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K61" s="15"/>
-      <c r="L61" s="15"/>
-      <c r="M61" s="15"/>
-      <c r="N61" s="16"/>
-    </row>
-    <row r="62" spans="1:14">
-      <c r="A62" s="12"/>
-      <c r="B62" s="13"/>
-      <c r="C62" s="13"/>
-      <c r="D62" s="13"/>
-      <c r="E62" s="13"/>
-      <c r="F62" s="13"/>
-      <c r="G62" s="13"/>
-      <c r="H62" s="13"/>
-      <c r="I62" s="14" t="str">
+        <v>400</v>
+      </c>
+      <c r="K61" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="L61" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M61" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="N61" s="16" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="62" ht="29" spans="1:14">
+      <c r="A62" s="12">
+        <v>46307</v>
+      </c>
+      <c r="B62" s="13">
+        <v>420</v>
+      </c>
+      <c r="C62" s="13">
+        <v>30</v>
+      </c>
+      <c r="D62" s="13">
+        <v>300</v>
+      </c>
+      <c r="E62" s="13">
+        <v>0</v>
+      </c>
+      <c r="F62" s="13">
+        <v>0</v>
+      </c>
+      <c r="G62" s="13">
+        <v>0</v>
+      </c>
+      <c r="H62" s="13">
+        <v>270</v>
+      </c>
+      <c r="I62" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="14" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J62" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K62" s="15"/>
-      <c r="L62" s="15"/>
-      <c r="M62" s="15"/>
-      <c r="N62" s="16"/>
-    </row>
-    <row r="63" spans="1:14">
-      <c r="A63" s="12"/>
-      <c r="B63" s="13"/>
-      <c r="C63" s="13"/>
-      <c r="D63" s="13"/>
-      <c r="E63" s="13"/>
-      <c r="F63" s="13"/>
-      <c r="G63" s="13"/>
-      <c r="H63" s="13"/>
-      <c r="I63" s="14" t="str">
+        <v>420</v>
+      </c>
+      <c r="K62" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="L62" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M62" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="N62" s="16" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="63" ht="29" spans="1:14">
+      <c r="A63" s="12">
+        <v>46308</v>
+      </c>
+      <c r="B63" s="13">
+        <v>360</v>
+      </c>
+      <c r="C63" s="13">
+        <v>30</v>
+      </c>
+      <c r="D63" s="13">
+        <v>360</v>
+      </c>
+      <c r="E63" s="13">
+        <v>0</v>
+      </c>
+      <c r="F63" s="13">
+        <v>0</v>
+      </c>
+      <c r="G63" s="13">
+        <v>0</v>
+      </c>
+      <c r="H63" s="13">
+        <v>320</v>
+      </c>
+      <c r="I63" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="14" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J63" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K63" s="15"/>
-      <c r="L63" s="15"/>
-      <c r="M63" s="15"/>
-      <c r="N63" s="16"/>
-    </row>
-    <row r="64" spans="1:14">
-      <c r="A64" s="12"/>
-      <c r="B64" s="13"/>
-      <c r="C64" s="13"/>
-      <c r="D64" s="13"/>
-      <c r="E64" s="13"/>
-      <c r="F64" s="13"/>
-      <c r="G64" s="13"/>
-      <c r="H64" s="13"/>
-      <c r="I64" s="14" t="str">
+        <v>370</v>
+      </c>
+      <c r="K63" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="L63" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="M63" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="N63" s="16" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="64" ht="29" spans="1:14">
+      <c r="A64" s="12">
+        <v>46309</v>
+      </c>
+      <c r="B64" s="13">
+        <v>300</v>
+      </c>
+      <c r="C64" s="13">
+        <v>30</v>
+      </c>
+      <c r="D64" s="13">
+        <v>420</v>
+      </c>
+      <c r="E64" s="13">
+        <v>0</v>
+      </c>
+      <c r="F64" s="13">
+        <v>0</v>
+      </c>
+      <c r="G64" s="13">
+        <v>0</v>
+      </c>
+      <c r="H64" s="13">
+        <v>270</v>
+      </c>
+      <c r="I64" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="14" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J64" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K64" s="15"/>
-      <c r="L64" s="15"/>
-      <c r="M64" s="15"/>
-      <c r="N64" s="16"/>
-    </row>
-    <row r="65" spans="1:14">
-      <c r="A65" s="12"/>
-      <c r="B65" s="13"/>
-      <c r="C65" s="13"/>
-      <c r="D65" s="13"/>
-      <c r="E65" s="13"/>
-      <c r="F65" s="13"/>
-      <c r="G65" s="13"/>
-      <c r="H65" s="13"/>
-      <c r="I65" s="14" t="str">
+        <v>420</v>
+      </c>
+      <c r="K64" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L64" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="M64" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="N64" s="16" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="65" ht="29" spans="1:14">
+      <c r="A65" s="12">
+        <v>46310</v>
+      </c>
+      <c r="B65" s="13">
+        <v>360</v>
+      </c>
+      <c r="C65" s="13">
+        <v>30</v>
+      </c>
+      <c r="D65" s="13">
+        <v>540</v>
+      </c>
+      <c r="E65" s="13">
+        <v>0</v>
+      </c>
+      <c r="F65" s="13">
+        <v>0</v>
+      </c>
+      <c r="G65" s="13">
+        <v>0</v>
+      </c>
+      <c r="H65" s="13">
+        <v>400</v>
+      </c>
+      <c r="I65" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="14" t="str">
+        <v>1330</v>
+      </c>
+      <c r="J65" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K65" s="15"/>
-      <c r="L65" s="15"/>
-      <c r="M65" s="15"/>
-      <c r="N65" s="16"/>
-    </row>
-    <row r="66" spans="1:14">
-      <c r="A66" s="12"/>
-      <c r="B66" s="13"/>
-      <c r="C66" s="13"/>
-      <c r="D66" s="13"/>
-      <c r="E66" s="13"/>
-      <c r="F66" s="13"/>
-      <c r="G66" s="13"/>
-      <c r="H66" s="13"/>
-      <c r="I66" s="14" t="str">
+        <v>110</v>
+      </c>
+      <c r="K65" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L65" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="M65" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="N65" s="16" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="66" ht="29" spans="1:14">
+      <c r="A66" s="12">
+        <v>46311</v>
+      </c>
+      <c r="B66" s="13">
+        <v>440</v>
+      </c>
+      <c r="C66" s="13">
+        <v>30</v>
+      </c>
+      <c r="D66" s="13">
+        <v>360</v>
+      </c>
+      <c r="E66" s="13">
+        <v>0</v>
+      </c>
+      <c r="F66" s="13">
+        <v>0</v>
+      </c>
+      <c r="G66" s="13">
+        <v>0</v>
+      </c>
+      <c r="H66" s="13">
+        <v>360</v>
+      </c>
+      <c r="I66" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="14" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J66" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K66" s="15"/>
-      <c r="L66" s="15"/>
-      <c r="M66" s="15"/>
-      <c r="N66" s="16"/>
-    </row>
-    <row r="67" spans="1:14">
-      <c r="A67" s="12"/>
-      <c r="B67" s="13"/>
-      <c r="C67" s="13"/>
-      <c r="D67" s="13"/>
-      <c r="E67" s="13"/>
-      <c r="F67" s="13"/>
-      <c r="G67" s="13"/>
-      <c r="H67" s="13"/>
-      <c r="I67" s="14" t="str">
+        <v>250</v>
+      </c>
+      <c r="K66" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L66" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M66" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="N66" s="16" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="67" ht="29" spans="1:14">
+      <c r="A67" s="12">
+        <v>46312</v>
+      </c>
+      <c r="B67" s="13">
+        <v>360</v>
+      </c>
+      <c r="C67" s="13">
+        <v>30</v>
+      </c>
+      <c r="D67" s="13">
+        <v>240</v>
+      </c>
+      <c r="E67" s="13">
+        <v>0</v>
+      </c>
+      <c r="F67" s="13">
+        <v>0</v>
+      </c>
+      <c r="G67" s="13">
+        <v>0</v>
+      </c>
+      <c r="H67" s="13">
+        <v>320</v>
+      </c>
+      <c r="I67" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J67" s="14" t="str">
+        <v>950</v>
+      </c>
+      <c r="J67" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K67" s="15"/>
-      <c r="L67" s="15"/>
-      <c r="M67" s="15"/>
-      <c r="N67" s="16"/>
+        <v>490</v>
+      </c>
+      <c r="K67" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L67" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="M67" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="N67" s="16" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="68" spans="1:14">
-      <c r="A68" s="12"/>
-      <c r="B68" s="13"/>
-      <c r="C68" s="13"/>
-      <c r="D68" s="13"/>
-      <c r="E68" s="13"/>
-      <c r="F68" s="13"/>
-      <c r="G68" s="13"/>
-      <c r="H68" s="13"/>
-      <c r="I68" s="14" t="str">
+      <c r="A68" s="12">
+        <v>46313</v>
+      </c>
+      <c r="B68" s="13">
+        <v>360</v>
+      </c>
+      <c r="C68" s="13">
+        <v>30</v>
+      </c>
+      <c r="D68" s="13">
+        <v>0</v>
+      </c>
+      <c r="E68" s="13">
+        <v>45</v>
+      </c>
+      <c r="F68" s="13">
+        <v>0</v>
+      </c>
+      <c r="G68" s="13">
+        <v>0</v>
+      </c>
+      <c r="H68" s="13">
+        <v>500</v>
+      </c>
+      <c r="I68" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J68" s="14" t="str">
+        <v>935</v>
+      </c>
+      <c r="J68" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K68" s="15"/>
-      <c r="L68" s="15"/>
-      <c r="M68" s="15"/>
-      <c r="N68" s="16"/>
-    </row>
-    <row r="69" spans="1:14">
-      <c r="A69" s="12"/>
-      <c r="B69" s="13"/>
-      <c r="C69" s="13"/>
-      <c r="D69" s="13"/>
-      <c r="E69" s="13"/>
-      <c r="F69" s="13"/>
-      <c r="G69" s="13"/>
-      <c r="H69" s="13"/>
-      <c r="I69" s="14" t="str">
+        <v>505</v>
+      </c>
+      <c r="K68" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="L68" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="M68" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="N68" s="16" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="69" ht="29" spans="1:14">
+      <c r="A69" s="12">
+        <v>46314</v>
+      </c>
+      <c r="B69" s="13">
+        <v>300</v>
+      </c>
+      <c r="C69" s="13">
+        <v>30</v>
+      </c>
+      <c r="D69" s="13">
+        <v>0</v>
+      </c>
+      <c r="E69" s="13">
+        <v>100</v>
+      </c>
+      <c r="F69" s="13">
+        <v>0</v>
+      </c>
+      <c r="G69" s="13">
+        <v>0</v>
+      </c>
+      <c r="H69" s="13">
+        <v>240</v>
+      </c>
+      <c r="I69" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J69" s="14" t="str">
+        <v>670</v>
+      </c>
+      <c r="J69" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K69" s="15"/>
-      <c r="L69" s="15"/>
-      <c r="M69" s="15"/>
-      <c r="N69" s="16"/>
-    </row>
-    <row r="70" spans="1:14">
-      <c r="A70" s="12"/>
-      <c r="B70" s="13"/>
-      <c r="C70" s="13"/>
-      <c r="D70" s="13"/>
-      <c r="E70" s="13"/>
-      <c r="F70" s="13"/>
-      <c r="G70" s="13"/>
-      <c r="H70" s="13"/>
-      <c r="I70" s="14" t="str">
+        <v>770</v>
+      </c>
+      <c r="K69" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="L69" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="M69" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="N69" s="16" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="70" ht="29" spans="1:14">
+      <c r="A70" s="12">
+        <v>46315</v>
+      </c>
+      <c r="B70" s="13">
+        <v>480</v>
+      </c>
+      <c r="C70" s="13">
+        <v>60</v>
+      </c>
+      <c r="D70" s="13">
+        <v>0</v>
+      </c>
+      <c r="E70" s="13">
+        <v>120</v>
+      </c>
+      <c r="F70" s="13">
+        <v>0</v>
+      </c>
+      <c r="G70" s="13">
+        <v>0</v>
+      </c>
+      <c r="H70" s="13">
+        <v>420</v>
+      </c>
+      <c r="I70" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J70" s="14" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J70" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K70" s="15"/>
-      <c r="L70" s="15"/>
-      <c r="M70" s="15"/>
-      <c r="N70" s="16"/>
+        <v>360</v>
+      </c>
+      <c r="K70" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="L70" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="M70" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="N70" s="16" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="71" spans="1:14">
-      <c r="A71" s="12"/>
-      <c r="B71" s="13"/>
-      <c r="C71" s="13"/>
-      <c r="D71" s="13"/>
-      <c r="E71" s="13"/>
-      <c r="F71" s="13"/>
-      <c r="G71" s="13"/>
-      <c r="H71" s="13"/>
-      <c r="I71" s="14" t="str">
+      <c r="A71" s="12">
+        <v>46316</v>
+      </c>
+      <c r="B71" s="13">
+        <v>300</v>
+      </c>
+      <c r="C71" s="13">
+        <v>45</v>
+      </c>
+      <c r="D71" s="13">
+        <v>0</v>
+      </c>
+      <c r="E71" s="13">
+        <v>0</v>
+      </c>
+      <c r="F71" s="13">
+        <v>0</v>
+      </c>
+      <c r="G71" s="13">
+        <v>0</v>
+      </c>
+      <c r="H71" s="13">
+        <v>240</v>
+      </c>
+      <c r="I71" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J71" s="14" t="str">
+        <v>585</v>
+      </c>
+      <c r="J71" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K71" s="15"/>
-      <c r="L71" s="15"/>
-      <c r="M71" s="15"/>
-      <c r="N71" s="16"/>
+        <v>855</v>
+      </c>
+      <c r="K71" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="L71" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M71" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="N71" s="16" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="72" spans="1:14">
-      <c r="A72" s="12"/>
-      <c r="B72" s="13"/>
-      <c r="C72" s="13"/>
-      <c r="D72" s="13"/>
-      <c r="E72" s="13"/>
-      <c r="F72" s="13"/>
-      <c r="G72" s="13"/>
-      <c r="H72" s="13"/>
-      <c r="I72" s="14" t="str">
+      <c r="A72" s="12">
+        <v>46317</v>
+      </c>
+      <c r="B72" s="13">
+        <v>420</v>
+      </c>
+      <c r="C72" s="13">
+        <v>30</v>
+      </c>
+      <c r="D72" s="13">
+        <v>0</v>
+      </c>
+      <c r="E72" s="13">
+        <v>60</v>
+      </c>
+      <c r="F72" s="13">
+        <v>350</v>
+      </c>
+      <c r="G72" s="13">
+        <v>7</v>
+      </c>
+      <c r="H72" s="13">
+        <v>160</v>
+      </c>
+      <c r="I72" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J72" s="14" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J72" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K72" s="15"/>
-      <c r="L72" s="15"/>
-      <c r="M72" s="15"/>
-      <c r="N72" s="16"/>
+        <v>420</v>
+      </c>
+      <c r="K72" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="L72" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="M72" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="N72" s="16" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="73" spans="1:14">
-      <c r="A73" s="12"/>
-      <c r="B73" s="13"/>
-      <c r="C73" s="13"/>
-      <c r="D73" s="13"/>
-      <c r="E73" s="13"/>
-      <c r="F73" s="13"/>
-      <c r="G73" s="13"/>
-      <c r="H73" s="13"/>
-      <c r="I73" s="14" t="str">
+      <c r="A73" s="12">
+        <v>46318</v>
+      </c>
+      <c r="B73" s="13">
+        <v>360</v>
+      </c>
+      <c r="C73" s="13">
+        <v>40</v>
+      </c>
+      <c r="D73" s="13">
+        <v>0</v>
+      </c>
+      <c r="E73" s="13">
+        <v>30</v>
+      </c>
+      <c r="F73" s="13">
+        <v>300</v>
+      </c>
+      <c r="G73" s="13">
+        <v>6</v>
+      </c>
+      <c r="H73" s="13">
+        <v>300</v>
+      </c>
+      <c r="I73" s="14">
         <f t="shared" ref="I73:I136" si="2">IF(SUM(B73:F73,H73)=0,"",SUM(B73:F73,H73))</f>
-        <v/>
-      </c>
-      <c r="J73" s="14" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J73" s="14">
         <f t="shared" ref="J73:J136" si="3">IF(I73="","",1440-I73)</f>
-        <v/>
-      </c>
-      <c r="K73" s="15"/>
-      <c r="L73" s="15"/>
-      <c r="M73" s="15"/>
-      <c r="N73" s="16"/>
+        <v>410</v>
+      </c>
+      <c r="K73" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="L73" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M73" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="N73" s="16" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="74" spans="1:14">
-      <c r="A74" s="12"/>
-      <c r="B74" s="13"/>
-      <c r="C74" s="13"/>
-      <c r="D74" s="13"/>
-      <c r="E74" s="13"/>
-      <c r="F74" s="13"/>
-      <c r="G74" s="13"/>
-      <c r="H74" s="13"/>
-      <c r="I74" s="14" t="str">
+      <c r="A74" s="12">
+        <v>46319</v>
+      </c>
+      <c r="B74" s="13">
+        <v>660</v>
+      </c>
+      <c r="C74" s="13">
+        <v>60</v>
+      </c>
+      <c r="D74" s="13">
+        <v>0</v>
+      </c>
+      <c r="E74" s="13">
+        <v>0</v>
+      </c>
+      <c r="F74" s="13">
+        <v>0</v>
+      </c>
+      <c r="G74" s="13">
+        <v>0</v>
+      </c>
+      <c r="H74" s="13">
+        <v>360</v>
+      </c>
+      <c r="I74" s="14">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J74" s="14" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J74" s="14">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K74" s="15"/>
-      <c r="L74" s="15"/>
-      <c r="M74" s="15"/>
-      <c r="N74" s="16"/>
-    </row>
-    <row r="75" spans="1:14">
-      <c r="A75" s="12"/>
-      <c r="B75" s="13"/>
-      <c r="C75" s="13"/>
-      <c r="D75" s="13"/>
-      <c r="E75" s="13"/>
-      <c r="F75" s="13"/>
-      <c r="G75" s="13"/>
-      <c r="H75" s="13"/>
-      <c r="I75" s="14" t="str">
+        <v>360</v>
+      </c>
+      <c r="K74" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="L74" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="M74" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="N74" s="16" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="75" ht="29" spans="1:14">
+      <c r="A75" s="12">
+        <v>46320</v>
+      </c>
+      <c r="B75" s="13">
+        <v>540</v>
+      </c>
+      <c r="C75" s="13">
+        <v>120</v>
+      </c>
+      <c r="D75" s="13">
+        <v>0</v>
+      </c>
+      <c r="E75" s="13">
+        <v>0</v>
+      </c>
+      <c r="F75" s="13">
+        <v>0</v>
+      </c>
+      <c r="G75" s="13">
+        <v>0</v>
+      </c>
+      <c r="H75" s="13">
+        <v>300</v>
+      </c>
+      <c r="I75" s="14">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J75" s="14" t="str">
+        <v>960</v>
+      </c>
+      <c r="J75" s="14">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K75" s="15"/>
-      <c r="L75" s="15"/>
-      <c r="M75" s="15"/>
-      <c r="N75" s="16"/>
+        <v>480</v>
+      </c>
+      <c r="K75" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="L75" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="M75" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="N75" s="16" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="76" spans="1:14">
       <c r="A76" s="12"/>
@@ -11824,13 +12304,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K54 K55:K57 K58:K404">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K404">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L54 L55:L57 L58:L404">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L404">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M54 M55:M57 M58:M404">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M404">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>
